--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9663,10 +9663,14 @@
       </c>
       <c r="F3" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/piWoV4Zx9wY</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" s="32">
       <c r="A4" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9698,10 +9698,14 @@
       </c>
       <c r="F4" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G4" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/maDijb1uzF8</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read Me &amp; Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Adult Riddles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Kids Riddles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Adult – Original" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Kids – Original" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me &amp; Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adult Riddles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kids Riddles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adult – Original" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kids – Original" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Adult Riddles'!$A$1:$I$1</definedName>
@@ -9628,14 +9628,10 @@
       </c>
       <c r="F2" s="55" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" s="57" t="inlineStr">
-        <is>
-          <t>https://youtu.be/nHgUWCiPPU8</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" s="57" t="n"/>
     </row>
     <row r="3" ht="31.5" customHeight="1" s="32">
       <c r="A3" s="58" t="n">
@@ -9663,14 +9659,10 @@
       </c>
       <c r="F3" s="58" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G3" s="60" t="inlineStr">
-        <is>
-          <t>https://youtu.be/piWoV4Zx9wY</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" s="60" t="n"/>
     </row>
     <row r="4" ht="31.5" customHeight="1" s="32">
       <c r="A4" s="55" t="n">
@@ -9698,14 +9690,10 @@
       </c>
       <c r="F4" s="55" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="57" t="inlineStr">
-        <is>
-          <t>https://youtu.be/maDijb1uzF8</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="57" t="n"/>
     </row>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="58" t="n">
@@ -10234,6 +10222,7 @@
       </c>
       <c r="G21" s="60" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="61" t="inlineStr">
         <is>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me &amp; Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adult Riddles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kids Riddles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adult – Original" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kids – Original" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read Me &amp; Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Adult Riddles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Kids Riddles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Adult – Original" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kids – Original" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Adult Riddles'!$A$1:$I$1</definedName>
@@ -9628,10 +9628,14 @@
       </c>
       <c r="F2" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G2" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/_ZQCoIy0KcY</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" s="32">
       <c r="A3" s="58" t="n">
@@ -10222,7 +10226,6 @@
       </c>
       <c r="G21" s="60" t="n"/>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="61" t="inlineStr">
         <is>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9663,10 +9663,14 @@
       </c>
       <c r="F3" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/yI98O6IJLn4</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" s="32">
       <c r="A4" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9698,10 +9698,14 @@
       </c>
       <c r="F4" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G4" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/KhZwxO-PIuc</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9733,10 +9733,14 @@
       </c>
       <c r="F5" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/qGNRy3M4lFg</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" s="32">
       <c r="A6" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9768,10 +9768,14 @@
       </c>
       <c r="F6" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G6" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/H4o7xlXCiD4</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="31.5" customHeight="1" s="32">
       <c r="A7" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9803,10 +9803,14 @@
       </c>
       <c r="F7" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G7" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/9gxph9Vs5CE</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="31.5" customHeight="1" s="32">
       <c r="A8" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9838,10 +9838,14 @@
       </c>
       <c r="F8" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G8" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GOgty3ZtPXY</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" s="32">
       <c r="A9" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9873,10 +9873,14 @@
       </c>
       <c r="F9" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G9" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Yi4fQH5uwRc</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="31.5" customHeight="1" s="32">
       <c r="A10" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9908,10 +9908,14 @@
       </c>
       <c r="F10" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G10" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rVOepfJ2W6s</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="31.5" customHeight="1" s="32">
       <c r="A11" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9943,10 +9943,14 @@
       </c>
       <c r="F11" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G11" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G11" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/MJbNwR7GKNo</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="31.5" customHeight="1" s="32">
       <c r="A12" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9978,10 +9978,14 @@
       </c>
       <c r="F12" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/FabDmi34aA0</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="31.5" customHeight="1" s="32">
       <c r="A13" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10013,10 +10013,14 @@
       </c>
       <c r="F13" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/SAID3z31Jl0</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="31.5" customHeight="1" s="32">
       <c r="A14" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10048,10 +10048,14 @@
       </c>
       <c r="F14" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/MXiQoinmQAw</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="31.5" customHeight="1" s="32">
       <c r="A15" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10083,10 +10083,14 @@
       </c>
       <c r="F15" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/9dsKzMvs6o8</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="31.5" customHeight="1" s="32">
       <c r="A16" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10118,10 +10118,14 @@
       </c>
       <c r="F16" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/6ouadxQXBCI</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="31.5" customHeight="1" s="32">
       <c r="A17" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10153,10 +10153,14 @@
       </c>
       <c r="F17" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/XalJ3kjogj0</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="31.5" customHeight="1" s="32">
       <c r="A18" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10188,10 +10188,14 @@
       </c>
       <c r="F18" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G18" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Ab97uqmDmD4</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="31.5" customHeight="1" s="32">
       <c r="A19" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10223,10 +10223,14 @@
       </c>
       <c r="F19" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/CfteLg6dAX0</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="31.5" customHeight="1" s="32">
       <c r="A20" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10258,10 +10258,14 @@
       </c>
       <c r="F20" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G20" s="57" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="57" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Du1niaAlFfg</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="31.5" customHeight="1" s="32">
       <c r="A21" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10293,10 +10293,14 @@
       </c>
       <c r="F21" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" s="60" t="inlineStr">
+        <is>
+          <t>https://youtu.be/fiDCj5WShS8</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="32">
       <c r="A23" s="61" t="inlineStr">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1181,10 +1181,14 @@
       </c>
       <c r="H2" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I2" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/XT_xRXpolf4</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="31.5" customHeight="1" s="32">
       <c r="A3" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1224,10 +1224,14 @@
       </c>
       <c r="H3" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I3" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/lJ7a0iWIjhs</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="31.5" customHeight="1" s="32">
       <c r="A4" s="55" t="n">
@@ -1263,10 +1267,14 @@
       </c>
       <c r="H4" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I4" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/qs2RDDThaf8</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" s="32">
       <c r="A5" s="58" t="n">
@@ -1302,10 +1310,14 @@
       </c>
       <c r="H5" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I5" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/dkodcH8-Mkk</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" s="32">
       <c r="A6" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1353,10 +1353,14 @@
       </c>
       <c r="H6" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I6" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VqVd546PhGw</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="31.5" customHeight="1" s="32">
       <c r="A7" s="58" t="n">
@@ -1392,10 +1396,14 @@
       </c>
       <c r="H7" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I7" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/js3iHeISfp0</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="31.5" customHeight="1" s="32">
       <c r="A8" s="55" t="n">
@@ -1431,10 +1439,14 @@
       </c>
       <c r="H8" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/4hjaLiO9jqw</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" s="32">
       <c r="A9" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1482,10 +1482,14 @@
       </c>
       <c r="H9" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I9" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UHYPdSEDzTw</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="31.5" customHeight="1" s="32">
       <c r="A10" s="55" t="n">
@@ -1521,10 +1525,14 @@
       </c>
       <c r="H10" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I10" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EyGAhUPU6j8</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="31.5" customHeight="1" s="32">
       <c r="A11" s="58" t="n">
@@ -1560,10 +1568,14 @@
       </c>
       <c r="H11" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I11" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/9O6sgOUZUHg</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="31.5" customHeight="1" s="32">
       <c r="A12" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1611,10 +1611,14 @@
       </c>
       <c r="H12" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I12" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cjGTI70FmKc</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="31.5" customHeight="1" s="32">
       <c r="A13" s="58" t="n">
@@ -1650,10 +1654,14 @@
       </c>
       <c r="H13" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I13" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/RHW_dZYpQfo</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="31.5" customHeight="1" s="32">
       <c r="A14" s="55" t="n">
@@ -1689,10 +1697,14 @@
       </c>
       <c r="H14" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I14" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UzGgy1-QL9M</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="31.5" customHeight="1" s="32">
       <c r="A15" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1740,10 +1740,14 @@
       </c>
       <c r="H15" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I15" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K_A_7HKWPpU</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="31.5" customHeight="1" s="32">
       <c r="A16" s="55" t="n">
@@ -1779,10 +1783,14 @@
       </c>
       <c r="H16" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I16" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/wEmD3FsOkg0</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="31.5" customHeight="1" s="32">
       <c r="A17" s="58" t="n">
@@ -1818,10 +1826,14 @@
       </c>
       <c r="H17" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I17" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/6rOLPfwcrlk</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="31.5" customHeight="1" s="32">
       <c r="A18" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1869,10 +1869,14 @@
       </c>
       <c r="H18" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I18" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nXc42sNMASQ</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="31.5" customHeight="1" s="32">
       <c r="A19" s="58" t="n">
@@ -1908,10 +1912,14 @@
       </c>
       <c r="H19" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I19" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jct5sv1TBB8</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="31.5" customHeight="1" s="32">
       <c r="A20" s="55" t="n">
@@ -1947,10 +1955,14 @@
       </c>
       <c r="H20" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I20" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/C66ZOZ_xKaQ</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="31.5" customHeight="1" s="32">
       <c r="A21" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1998,10 +1998,14 @@
       </c>
       <c r="H21" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I21" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q3lReLLUTpc</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="31.5" customHeight="1" s="32">
       <c r="A22" s="55" t="n">
@@ -2037,10 +2041,14 @@
       </c>
       <c r="H22" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I22" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/TxVRPqzjvaA</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="31.5" customHeight="1" s="32">
       <c r="A23" s="58" t="n">
@@ -2076,10 +2084,14 @@
       </c>
       <c r="H23" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I23" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/epKkWoJPPuM</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="31.5" customHeight="1" s="32">
       <c r="A24" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -2127,10 +2127,14 @@
       </c>
       <c r="H24" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I24" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/wVMYMe8xp2I</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="31.5" customHeight="1" s="32">
       <c r="A25" s="58" t="n">
@@ -2166,10 +2170,14 @@
       </c>
       <c r="H25" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I25" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BOypdWoAeLg</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="31.5" customHeight="1" s="32">
       <c r="A26" s="55" t="n">
@@ -2205,10 +2213,14 @@
       </c>
       <c r="H26" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I26" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/RLT5ogUw7Vg</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="31.5" customHeight="1" s="32">
       <c r="A27" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -2256,10 +2256,14 @@
       </c>
       <c r="H27" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I27" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I27" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nKhznimuAIQ</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="31.5" customHeight="1" s="32">
       <c r="A28" s="55" t="n">
@@ -2295,10 +2299,14 @@
       </c>
       <c r="H28" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I28" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I28" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Gb6SC92z3hM</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="31.5" customHeight="1" s="32">
       <c r="A29" s="58" t="n">
@@ -2334,10 +2342,14 @@
       </c>
       <c r="H29" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I29" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/H4RC1Lz2CV0</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="31.5" customHeight="1" s="32">
       <c r="A30" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -2385,10 +2385,14 @@
       </c>
       <c r="H30" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I30" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/J1HEwk0areE</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="31.5" customHeight="1" s="32">
       <c r="A31" s="58" t="n">
@@ -2424,10 +2428,14 @@
       </c>
       <c r="H31" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I31" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/dTeGMFq-f9M</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="31.5" customHeight="1" s="32">
       <c r="A32" s="55" t="n">
@@ -2463,10 +2471,14 @@
       </c>
       <c r="H32" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I32" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I32" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/lYZ4S1BVKrY</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="31.5" customHeight="1" s="32">
       <c r="A33" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -2514,10 +2514,14 @@
       </c>
       <c r="H33" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I33" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/XAAqaFqSFCY</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="31.5" customHeight="1" s="32">
       <c r="A34" s="55" t="n">
@@ -2553,10 +2557,14 @@
       </c>
       <c r="H34" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I34" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I34" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aFwpwrGOVHk</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="31.5" customHeight="1" s="32">
       <c r="A35" s="58" t="n">
@@ -2592,10 +2600,14 @@
       </c>
       <c r="H35" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I35" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I35" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8iTA2QL7epo</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="31.5" customHeight="1" s="32">
       <c r="A36" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -2643,10 +2643,14 @@
       </c>
       <c r="H36" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I36" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Pd3h1S1q39A</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="31.5" customHeight="1" s="32">
       <c r="A37" s="58" t="n">
@@ -2682,10 +2686,14 @@
       </c>
       <c r="H37" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I37" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/apZ2-a2sX3U</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="31.5" customHeight="1" s="32">
       <c r="A38" s="55" t="n">
@@ -2721,10 +2729,14 @@
       </c>
       <c r="H38" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I38" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I38" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jn1A3yB3nEk</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="31.5" customHeight="1" s="32">
       <c r="A39" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -2772,10 +2772,14 @@
       </c>
       <c r="H39" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I39" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I39" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/0dopdCitaQg</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="31.5" customHeight="1" s="32">
       <c r="A40" s="55" t="n">
@@ -2811,10 +2815,14 @@
       </c>
       <c r="H40" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I40" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I40" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/yzK8W4yu_rc</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="31.5" customHeight="1" s="32">
       <c r="A41" s="58" t="n">
@@ -2850,10 +2858,14 @@
       </c>
       <c r="H41" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I41" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I41" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Up5i5ZsqFS8</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="31.5" customHeight="1" s="32">
       <c r="A42" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -2901,10 +2901,14 @@
       </c>
       <c r="H42" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I42" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I42" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/9hRKL5rDtgc</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="31.5" customHeight="1" s="32">
       <c r="A43" s="58" t="n">
@@ -2940,10 +2944,14 @@
       </c>
       <c r="H43" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I43" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I43" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tOEjNQmfSHo</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="31.5" customHeight="1" s="32">
       <c r="A44" s="55" t="n">
@@ -2979,10 +2987,14 @@
       </c>
       <c r="H44" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I44" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I44" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/jwghbP_4fwo</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="31.5" customHeight="1" s="32">
       <c r="A45" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3030,10 +3030,14 @@
       </c>
       <c r="H45" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I45" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I45" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LV2QVAICv8w</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="31.5" customHeight="1" s="32">
       <c r="A46" s="55" t="n">
@@ -3069,10 +3073,14 @@
       </c>
       <c r="H46" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I46" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I46" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2FkMYNoJLWA</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="31.5" customHeight="1" s="32">
       <c r="A47" s="58" t="n">
@@ -3108,10 +3116,14 @@
       </c>
       <c r="H47" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I47" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I47" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ZplE3UQ3w_o</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="31.5" customHeight="1" s="32">
       <c r="A48" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3159,10 +3159,14 @@
       </c>
       <c r="H48" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I48" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I48" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GxzRiCIsQTk</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="31.5" customHeight="1" s="32">
       <c r="A49" s="58" t="n">
@@ -3198,10 +3202,14 @@
       </c>
       <c r="H49" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I49" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I49" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/90OG7rOaaus</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="31.5" customHeight="1" s="32">
       <c r="A50" s="55" t="n">
@@ -3237,10 +3245,14 @@
       </c>
       <c r="H50" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I50" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I50" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/i21eB3l5a_Y</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="31.5" customHeight="1" s="32">
       <c r="A51" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3288,10 +3288,14 @@
       </c>
       <c r="H51" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I51" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I51" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/AXI4yRyqsdg</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="31.5" customHeight="1" s="32">
       <c r="A52" s="55" t="n">
@@ -3327,10 +3331,14 @@
       </c>
       <c r="H52" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I52" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I52" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/5dnte62syjg</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="31.5" customHeight="1" s="32">
       <c r="A53" s="58" t="n">
@@ -3366,10 +3374,14 @@
       </c>
       <c r="H53" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I53" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I53" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/j463YwykBX0</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="31.5" customHeight="1" s="32">
       <c r="A54" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3417,10 +3417,14 @@
       </c>
       <c r="H54" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I54" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I54" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ALFZnUGaIoE</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="31.5" customHeight="1" s="32">
       <c r="A55" s="58" t="n">
@@ -3456,10 +3460,14 @@
       </c>
       <c r="H55" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I55" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I55" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/FAWF5MgRjlo</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="31.5" customHeight="1" s="32">
       <c r="A56" s="55" t="n">
@@ -3495,10 +3503,14 @@
       </c>
       <c r="H56" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I56" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I56" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/5NQU_P2ZaRU</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="31.5" customHeight="1" s="32">
       <c r="A57" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3546,10 +3546,14 @@
       </c>
       <c r="H57" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I57" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I57" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/4SKmc2cl4aY</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="31.5" customHeight="1" s="32">
       <c r="A58" s="55" t="n">
@@ -3585,10 +3589,14 @@
       </c>
       <c r="H58" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I58" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I58" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cAi1KJB1xNs</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="31.5" customHeight="1" s="32">
       <c r="A59" s="58" t="n">
@@ -3624,10 +3632,14 @@
       </c>
       <c r="H59" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I59" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I59" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/kNRB3TDRDGs</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="31.5" customHeight="1" s="32">
       <c r="A60" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3675,10 +3675,14 @@
       </c>
       <c r="H60" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I60" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I60" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/FyYZqcLoRHE</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="31.5" customHeight="1" s="32">
       <c r="A61" s="58" t="n">
@@ -3714,10 +3718,14 @@
       </c>
       <c r="H61" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I61" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I61" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/zHIwt3-OUGo</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="31.5" customHeight="1" s="32">
       <c r="A62" s="55" t="n">
@@ -3753,10 +3761,14 @@
       </c>
       <c r="H62" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I62" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/-jN81FlwUo8</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="31.5" customHeight="1" s="32">
       <c r="A63" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3804,10 +3804,14 @@
       </c>
       <c r="H63" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I63" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I63" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cxcilMcfic8</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="31.5" customHeight="1" s="32">
       <c r="A64" s="55" t="n">
@@ -3843,10 +3847,14 @@
       </c>
       <c r="H64" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I64" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/IfGwJJ_7MDw</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="31.5" customHeight="1" s="32">
       <c r="A65" s="58" t="n">
@@ -3882,10 +3890,14 @@
       </c>
       <c r="H65" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I65" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I65" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/oaOVjKWaCf0</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="31.5" customHeight="1" s="32">
       <c r="A66" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -3933,10 +3933,14 @@
       </c>
       <c r="H66" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I66" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I66" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/phZNpf14LN8</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="31.5" customHeight="1" s="32">
       <c r="A67" s="58" t="n">
@@ -3972,10 +3976,14 @@
       </c>
       <c r="H67" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I67" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I67" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/vJcHFJ4DUSQ</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="31.5" customHeight="1" s="32">
       <c r="A68" s="55" t="n">
@@ -4011,10 +4019,14 @@
       </c>
       <c r="H68" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I68" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I68" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/94gVwMe8r7c</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="31.5" customHeight="1" s="32">
       <c r="A69" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4062,10 +4062,14 @@
       </c>
       <c r="H69" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I69" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I69" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/PdEhTHEU9Cg</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="31.5" customHeight="1" s="32">
       <c r="A70" s="55" t="n">
@@ -4101,10 +4105,14 @@
       </c>
       <c r="H70" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I70" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I70" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/byiNuG_aR5s</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="31.5" customHeight="1" s="32">
       <c r="A71" s="58" t="n">
@@ -4140,10 +4148,14 @@
       </c>
       <c r="H71" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I71" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I71" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/KXNu7XG6mac</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="31.5" customHeight="1" s="32">
       <c r="A72" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4191,10 +4191,14 @@
       </c>
       <c r="H72" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I72" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I72" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/vL0HvbFUI-c</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="31.5" customHeight="1" s="32">
       <c r="A73" s="58" t="n">
@@ -4230,10 +4234,14 @@
       </c>
       <c r="H73" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I73" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I73" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ACG4tvnu9jc</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="31.5" customHeight="1" s="32">
       <c r="A74" s="55" t="n">
@@ -4269,10 +4277,14 @@
       </c>
       <c r="H74" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I74" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I74" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/JfdSOfNkPxw</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="31.5" customHeight="1" s="32">
       <c r="A75" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4320,10 +4320,14 @@
       </c>
       <c r="H75" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I75" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I75" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VNmMIW2fEjc</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="31.5" customHeight="1" s="32">
       <c r="A76" s="55" t="n">
@@ -4359,10 +4363,14 @@
       </c>
       <c r="H76" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I76" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I76" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/1uTGqdmbVyw</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="31.5" customHeight="1" s="32">
       <c r="A77" s="58" t="n">
@@ -4398,10 +4406,14 @@
       </c>
       <c r="H77" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I77" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I77" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/uLqBpmVhiu0</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="31.5" customHeight="1" s="32">
       <c r="A78" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4449,10 +4449,14 @@
       </c>
       <c r="H78" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I78" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I78" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ja0rSGTW6xA</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="31.5" customHeight="1" s="32">
       <c r="A79" s="58" t="n">
@@ -4488,10 +4492,14 @@
       </c>
       <c r="H79" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I79" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I79" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tg7rnDiiJhw</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="31.5" customHeight="1" s="32">
       <c r="A80" s="55" t="n">
@@ -4527,10 +4535,14 @@
       </c>
       <c r="H80" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I80" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I80" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/4XwO0UEH0Pw</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="31.5" customHeight="1" s="32">
       <c r="A81" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4578,10 +4578,14 @@
       </c>
       <c r="H81" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I81" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I81" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/RcDLcke5oz4</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="31.5" customHeight="1" s="32">
       <c r="A82" s="55" t="n">
@@ -4617,10 +4621,14 @@
       </c>
       <c r="H82" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I82" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I82" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/m0FQhB5Sg-M</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="31.5" customHeight="1" s="32">
       <c r="A83" s="58" t="n">
@@ -4656,10 +4664,14 @@
       </c>
       <c r="H83" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I83" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I83" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Jbzgufs3zZk</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="31.5" customHeight="1" s="32">
       <c r="A84" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4707,10 +4707,14 @@
       </c>
       <c r="H84" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I84" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I84" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2w75p8AXpn0</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="31.5" customHeight="1" s="32">
       <c r="A85" s="58" t="n">
@@ -4746,10 +4750,14 @@
       </c>
       <c r="H85" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I85" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I85" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/6jf8VNBBZFU</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="31.5" customHeight="1" s="32">
       <c r="A86" s="55" t="n">
@@ -4785,10 +4793,14 @@
       </c>
       <c r="H86" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I86" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I86" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/btm7RJWd86U</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="31.5" customHeight="1" s="32">
       <c r="A87" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4836,10 +4836,14 @@
       </c>
       <c r="H87" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I87" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I87" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/j2c6iPF8jUU</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="31.5" customHeight="1" s="32">
       <c r="A88" s="55" t="n">
@@ -4875,10 +4879,14 @@
       </c>
       <c r="H88" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I88" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I88" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/hT6lYcTWJ7Q</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="31.5" customHeight="1" s="32">
       <c r="A89" s="58" t="n">
@@ -4914,10 +4922,14 @@
       </c>
       <c r="H89" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I89" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I89" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/3NtrKeohBnE</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="31.5" customHeight="1" s="32">
       <c r="A90" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -4965,10 +4965,14 @@
       </c>
       <c r="H90" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I90" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I90" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/askNfBOJvhA</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="31.5" customHeight="1" s="32">
       <c r="A91" s="58" t="n">
@@ -5004,10 +5008,14 @@
       </c>
       <c r="H91" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I91" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I91" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/M6NXvAfZZ0s</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="31.5" customHeight="1" s="32">
       <c r="A92" s="55" t="n">
@@ -5043,10 +5051,14 @@
       </c>
       <c r="H92" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I92" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I92" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ChRhDm1ZPFU</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="31.5" customHeight="1" s="32">
       <c r="A93" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -5094,10 +5094,14 @@
       </c>
       <c r="H93" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I93" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I93" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/hxWD5YNSNpw</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="31.5" customHeight="1" s="32">
       <c r="A94" s="55" t="n">
@@ -5133,10 +5137,14 @@
       </c>
       <c r="H94" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I94" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I94" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nxuqZKmXqco</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="31.5" customHeight="1" s="32">
       <c r="A95" s="58" t="n">
@@ -5172,10 +5180,14 @@
       </c>
       <c r="H95" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I95" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I95" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/1dnksaLOvis</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="31.5" customHeight="1" s="32">
       <c r="A96" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -5223,10 +5223,14 @@
       </c>
       <c r="H96" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I96" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I96" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VNColounGWU</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="31.5" customHeight="1" s="32">
       <c r="A97" s="58" t="n">
@@ -5262,10 +5266,14 @@
       </c>
       <c r="H97" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I97" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I97" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YxdEIox-7Iw</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="31.5" customHeight="1" s="32">
       <c r="A98" s="55" t="n">
@@ -5301,10 +5309,14 @@
       </c>
       <c r="H98" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I98" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I98" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nq7PGYFXrjc</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="31.5" customHeight="1" s="32">
       <c r="A99" s="58" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -5352,10 +5352,14 @@
       </c>
       <c r="H99" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I99" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I99" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GYSZ9t7gIPM</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="31.5" customHeight="1" s="32">
       <c r="A100" s="55" t="n">
@@ -5391,10 +5395,14 @@
       </c>
       <c r="H100" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I100" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I100" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rN2L_pR-Tng</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="31.5" customHeight="1" s="32">
       <c r="A101" s="58" t="n">
@@ -5430,10 +5438,14 @@
       </c>
       <c r="H101" s="58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I101" s="58" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I101" s="58" t="inlineStr">
+        <is>
+          <t>https://youtu.be/xyD_HGsaY4s</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -5610,10 +5610,14 @@
       </c>
       <c r="H105" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I105" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I105" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cLwGkw4hvug</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="23.85" customHeight="1" s="32">
       <c r="A106" s="55" t="n">
@@ -5649,10 +5653,14 @@
       </c>
       <c r="H106" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I106" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I106" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/HhFVGb2LnC4</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="32">
       <c r="A107" s="55" t="n">
@@ -5688,10 +5696,14 @@
       </c>
       <c r="H107" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I107" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I107" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/DgYFtqv0xUs</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="32">
       <c r="A108" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -5739,10 +5739,14 @@
       </c>
       <c r="H108" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I108" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I108" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/DiawrJRg3y0</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="32">
       <c r="A109" s="55" t="n">
@@ -5778,10 +5782,14 @@
       </c>
       <c r="H109" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I109" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I109" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/xIvquevlSiw</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="32">
       <c r="A110" s="55" t="n">
@@ -5817,10 +5825,14 @@
       </c>
       <c r="H110" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I110" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I110" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/pZLDMY7Vc8k</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="23.85" customHeight="1" s="32">
       <c r="A111" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -5868,10 +5868,14 @@
       </c>
       <c r="H111" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I111" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I111" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K56GnXjxJ5c</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="23.85" customHeight="1" s="32">
       <c r="A112" s="55" t="n">
@@ -5907,10 +5911,14 @@
       </c>
       <c r="H112" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I112" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I112" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ifIyi804WUI</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="23.85" customHeight="1" s="32">
       <c r="A113" s="55" t="n">
@@ -5946,10 +5954,14 @@
       </c>
       <c r="H113" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I113" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I113" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/CeQ4_hR7erk</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="23.85" customHeight="1" s="32">
       <c r="A114" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -5997,10 +5997,14 @@
       </c>
       <c r="H114" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I114" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I114" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/DfGDQOTG02k</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="23.85" customHeight="1" s="32">
       <c r="A115" s="55" t="n">
@@ -6036,10 +6040,14 @@
       </c>
       <c r="H115" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I115" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I115" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/pmC61rF-ZNQ</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="32">
       <c r="A116" s="55" t="n">
@@ -6075,10 +6083,14 @@
       </c>
       <c r="H116" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I116" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I116" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/CmG0hANQTtA</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="23.85" customHeight="1" s="32">
       <c r="A117" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -6126,10 +6126,14 @@
       </c>
       <c r="H117" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I117" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I117" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/3jvNG5ULp2U</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="23.85" customHeight="1" s="32">
       <c r="A118" s="55" t="n">
@@ -6165,10 +6169,14 @@
       </c>
       <c r="H118" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I118" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I118" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8hKdGIY1KRs</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="23.85" customHeight="1" s="32">
       <c r="A119" s="55" t="n">
@@ -6204,10 +6212,14 @@
       </c>
       <c r="H119" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I119" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I119" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2yiXS4yiWXw</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1" s="32">
       <c r="A120" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -6255,10 +6255,14 @@
       </c>
       <c r="H120" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I120" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I120" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/4EwSWhPMPhc</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="23.85" customHeight="1" s="32">
       <c r="A121" s="55" t="n">
@@ -6294,10 +6298,14 @@
       </c>
       <c r="H121" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I121" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I121" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/gSQxi_LZviM</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1" s="32">
       <c r="A122" s="55" t="n">
@@ -6333,10 +6341,14 @@
       </c>
       <c r="H122" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I122" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I122" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EfOBadDcREQ</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1" s="32">
       <c r="A123" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -6384,10 +6384,14 @@
       </c>
       <c r="H123" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I123" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I123" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ItXiYz8De2k</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1" s="32">
       <c r="A124" s="55" t="n">
@@ -6423,10 +6427,14 @@
       </c>
       <c r="H124" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I124" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I124" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Qrb_5_muY3A</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="32">
       <c r="A125" s="55" t="n">
@@ -6462,10 +6470,14 @@
       </c>
       <c r="H125" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I125" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I125" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/hZj1mUg3mdI</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="23.85" customHeight="1" s="32">
       <c r="A126" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -6513,10 +6513,14 @@
       </c>
       <c r="H126" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I126" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I126" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/vwIJ-Uk330k</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="23.85" customHeight="1" s="32">
       <c r="A127" s="55" t="n">
@@ -6552,10 +6556,14 @@
       </c>
       <c r="H127" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I127" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I127" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/6VZ2e9rMhWg</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="23.85" customHeight="1" s="32">
       <c r="A128" s="55" t="n">
@@ -6591,10 +6599,14 @@
       </c>
       <c r="H128" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I128" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I128" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/oul1uvzJXl8</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1" s="32">
       <c r="A129" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -6642,10 +6642,14 @@
       </c>
       <c r="H129" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I129" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I129" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/71upArDa6F0</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="32">
       <c r="A130" s="55" t="n">
@@ -6681,10 +6685,14 @@
       </c>
       <c r="H130" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I130" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I130" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/FJS9qwkeMiU</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="23.85" customHeight="1" s="32">
       <c r="A131" s="55" t="n">
@@ -6720,10 +6728,14 @@
       </c>
       <c r="H131" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I131" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I131" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/oGVc5qlGj7A</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="32">
       <c r="A132" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -6771,10 +6771,14 @@
       </c>
       <c r="H132" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I132" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I132" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/5g6Is9Cex7w</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="32">
       <c r="A133" s="55" t="n">
@@ -6810,10 +6814,14 @@
       </c>
       <c r="H133" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I133" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I133" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Ox03ci9cx5U</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="23.85" customHeight="1" s="32">
       <c r="A134" s="55" t="n">
@@ -6849,10 +6857,14 @@
       </c>
       <c r="H134" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I134" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I134" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/5EU9FoYZ_m0</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="32">
       <c r="A135" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -6900,10 +6900,14 @@
       </c>
       <c r="H135" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I135" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I135" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/w5xQgrx3sJ0</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="23.85" customHeight="1" s="32">
       <c r="A136" s="55" t="n">
@@ -6939,10 +6943,14 @@
       </c>
       <c r="H136" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I136" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I136" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8D5ThvY-6Xc</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="23.85" customHeight="1" s="32">
       <c r="A137" s="55" t="n">
@@ -6978,10 +6986,14 @@
       </c>
       <c r="H137" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I137" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I137" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cTY6tCJmzxw</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="23.85" customHeight="1" s="32">
       <c r="A138" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7029,10 +7029,14 @@
       </c>
       <c r="H138" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I138" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I138" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/fpX-d3TOQbM</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="32">
       <c r="A139" s="55" t="n">
@@ -7068,10 +7072,14 @@
       </c>
       <c r="H139" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I139" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I139" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/3jJ6DpKcrSk</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="23.85" customHeight="1" s="32">
       <c r="A140" s="55" t="n">
@@ -7107,10 +7115,14 @@
       </c>
       <c r="H140" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I140" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I140" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/PBdrYvEvHbM</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="23.85" customHeight="1" s="32">
       <c r="A141" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7158,10 +7158,14 @@
       </c>
       <c r="H141" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I141" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I141" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2WAEkKeWZqk</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="32">
       <c r="A142" s="55" t="n">
@@ -7197,10 +7201,14 @@
       </c>
       <c r="H142" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I142" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I142" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/f4MVxhsBmWI</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15" customHeight="1" s="32">
       <c r="A143" s="55" t="n">
@@ -7236,10 +7244,14 @@
       </c>
       <c r="H143" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I143" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I143" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8w3Rk6UOhkg</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="23.85" customHeight="1" s="32">
       <c r="A144" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7287,10 +7287,14 @@
       </c>
       <c r="H144" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I144" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I144" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/_qKaVEwLeiI</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="32">
       <c r="A145" s="55" t="n">
@@ -7326,10 +7330,14 @@
       </c>
       <c r="H145" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I145" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I145" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/fDOQTbUqCDM</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15" customHeight="1" s="32">
       <c r="A146" s="55" t="n">
@@ -7365,10 +7373,14 @@
       </c>
       <c r="H146" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I146" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I146" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ttJIlQ6EUnw</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15" customHeight="1" s="32">
       <c r="A147" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7416,10 +7416,14 @@
       </c>
       <c r="H147" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I147" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I147" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LGJgBXN8XAI</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="32">
       <c r="A148" s="55" t="n">
@@ -7455,10 +7459,14 @@
       </c>
       <c r="H148" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I148" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I148" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UyslTDVJWGg</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="32">
       <c r="A149" s="55" t="n">
@@ -7494,10 +7502,14 @@
       </c>
       <c r="H149" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I149" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I149" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tyoyNa-5TLs</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="23.85" customHeight="1" s="32">
       <c r="A150" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7545,10 +7545,14 @@
       </c>
       <c r="H150" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I150" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I150" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/z087URPZZdA</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="32">
       <c r="A151" s="55" t="n">
@@ -7584,10 +7588,14 @@
       </c>
       <c r="H151" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I151" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I151" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/4Gd4ISsafpI</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="23.85" customHeight="1" s="32">
       <c r="A152" s="55" t="n">
@@ -7623,10 +7631,14 @@
       </c>
       <c r="H152" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I152" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I152" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GLAnNt32pr0</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="32">
       <c r="A153" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7674,10 +7674,14 @@
       </c>
       <c r="H153" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I153" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I153" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nAYi8xN0PMA</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="23.85" customHeight="1" s="32">
       <c r="A154" s="55" t="n">
@@ -7713,10 +7717,14 @@
       </c>
       <c r="H154" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I154" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I154" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/CTRxkQwdxAM</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="32">
       <c r="A155" s="55" t="n">
@@ -7752,10 +7760,14 @@
       </c>
       <c r="H155" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I155" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I155" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ZbSY2p4F5AU</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="23.85" customHeight="1" s="32">
       <c r="A156" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7803,10 +7803,14 @@
       </c>
       <c r="H156" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I156" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I156" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/iAAYUamGocY</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="23.85" customHeight="1" s="32">
       <c r="A157" s="55" t="n">
@@ -7842,10 +7846,14 @@
       </c>
       <c r="H157" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I157" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I157" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/1mTSoiRuKxk</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="23.85" customHeight="1" s="32">
       <c r="A158" s="55" t="n">
@@ -7881,10 +7889,14 @@
       </c>
       <c r="H158" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I158" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I158" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nsMbpZssslc</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="32">
       <c r="A159" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -7932,10 +7932,14 @@
       </c>
       <c r="H159" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I159" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I159" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/uHz6YvP3n6I</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1" s="32">
       <c r="A160" s="55" t="n">
@@ -7971,10 +7975,14 @@
       </c>
       <c r="H160" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I160" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I160" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7N3TMInvSlc</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="23.85" customHeight="1" s="32">
       <c r="A161" s="55" t="n">
@@ -8010,10 +8018,14 @@
       </c>
       <c r="H161" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I161" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I161" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/93of1biImB0</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="15" customHeight="1" s="32">
       <c r="A162" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8061,10 +8061,14 @@
       </c>
       <c r="H162" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I162" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I162" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/varu1sAPkNg</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="23.85" customHeight="1" s="32">
       <c r="A163" s="55" t="n">
@@ -8100,10 +8104,14 @@
       </c>
       <c r="H163" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I163" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I163" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/pG8CzUX7nW0</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="23.85" customHeight="1" s="32">
       <c r="A164" s="55" t="n">
@@ -8139,10 +8147,14 @@
       </c>
       <c r="H164" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I164" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I164" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/CoQ1lcCyCLA</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="23.85" customHeight="1" s="32">
       <c r="A165" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8190,10 +8190,14 @@
       </c>
       <c r="H165" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I165" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I165" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Oz30fK1lEd8</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="15" customHeight="1" s="32">
       <c r="A166" s="55" t="n">
@@ -8229,10 +8233,14 @@
       </c>
       <c r="H166" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I166" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I166" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GidakqLcsnM</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="23.85" customHeight="1" s="32">
       <c r="A167" s="55" t="n">
@@ -8268,10 +8276,14 @@
       </c>
       <c r="H167" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I167" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I167" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UxAeZcLEWE8</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="23.85" customHeight="1" s="32">
       <c r="A168" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8319,10 +8319,14 @@
       </c>
       <c r="H168" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I168" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I168" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7Z3Huqn6muE</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="23.85" customHeight="1" s="32">
       <c r="A169" s="55" t="n">
@@ -8358,10 +8362,14 @@
       </c>
       <c r="H169" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I169" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I169" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/xz9AO3sw8g4</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1" s="32">
       <c r="A170" s="55" t="n">
@@ -8397,10 +8405,14 @@
       </c>
       <c r="H170" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I170" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I170" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V-XxTh6J9pc</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="23.85" customHeight="1" s="32">
       <c r="A171" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8448,10 +8448,14 @@
       </c>
       <c r="H171" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I171" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I171" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/KWeBdIqjDLY</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="15" customHeight="1" s="32">
       <c r="A172" s="55" t="n">
@@ -8487,10 +8491,14 @@
       </c>
       <c r="H172" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I172" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I172" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7ZFOIK8xdOc</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="15" customHeight="1" s="32">
       <c r="A173" s="55" t="n">
@@ -8526,10 +8534,14 @@
       </c>
       <c r="H173" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I173" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I173" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y6Bv9-QiAuU</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="23.85" customHeight="1" s="32">
       <c r="A174" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8577,10 +8577,14 @@
       </c>
       <c r="H174" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I174" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I174" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tJYi-CKtwWc</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="23.85" customHeight="1" s="32">
       <c r="A175" s="55" t="n">
@@ -8616,10 +8620,14 @@
       </c>
       <c r="H175" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I175" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I175" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2QdutAwtTQI</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="23.85" customHeight="1" s="32">
       <c r="A176" s="55" t="n">
@@ -8655,10 +8663,14 @@
       </c>
       <c r="H176" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I176" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I176" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VMeLKtNBqfc</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="23.85" customHeight="1" s="32">
       <c r="A177" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8706,10 +8706,14 @@
       </c>
       <c r="H177" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I177" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I177" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/KAJeWIYxFIQ</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="23.85" customHeight="1" s="32">
       <c r="A178" s="55" t="n">
@@ -8745,10 +8749,14 @@
       </c>
       <c r="H178" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I178" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I178" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8fsdP2K7NSE</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="23.85" customHeight="1" s="32">
       <c r="A179" s="55" t="n">
@@ -8784,10 +8792,14 @@
       </c>
       <c r="H179" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I179" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I179" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/gatFPEjfYH0</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="23.85" customHeight="1" s="32">
       <c r="A180" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8835,10 +8835,14 @@
       </c>
       <c r="H180" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I180" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I180" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ZWnzlFz2nCM</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="23.85" customHeight="1" s="32">
       <c r="A181" s="55" t="n">
@@ -8874,10 +8878,14 @@
       </c>
       <c r="H181" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I181" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I181" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/PIFBUHj6yV0</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="23.85" customHeight="1" s="32">
       <c r="A182" s="55" t="n">
@@ -8913,10 +8921,14 @@
       </c>
       <c r="H182" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I182" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I182" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nkHWQ3dRORA</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="23.85" customHeight="1" s="32">
       <c r="A183" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -8964,10 +8964,14 @@
       </c>
       <c r="H183" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I183" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I183" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Ca3X3QjAkjI</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="23.85" customHeight="1" s="32">
       <c r="A184" s="55" t="n">
@@ -9003,10 +9007,14 @@
       </c>
       <c r="H184" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I184" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I184" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/epoNfsBRLso</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="23.85" customHeight="1" s="32">
       <c r="A185" s="55" t="n">
@@ -9042,10 +9050,14 @@
       </c>
       <c r="H185" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I185" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I185" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/2jg_M3yI1Vk</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="23.85" customHeight="1" s="32">
       <c r="A186" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9093,10 +9093,14 @@
       </c>
       <c r="H186" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I186" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I186" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/sifOXxkE7vI</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="23.85" customHeight="1" s="32">
       <c r="A187" s="55" t="n">
@@ -9132,10 +9136,14 @@
       </c>
       <c r="H187" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I187" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I187" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/lPFGwcdvhUs</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="23.85" customHeight="1" s="32">
       <c r="A188" s="55" t="n">
@@ -9171,10 +9179,14 @@
       </c>
       <c r="H188" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I188" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I188" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Hchcuo8X_rg</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="15" customHeight="1" s="32">
       <c r="A189" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9222,10 +9222,14 @@
       </c>
       <c r="H189" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I189" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I189" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UzK9of8H8sg</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1" s="32">
       <c r="A190" s="55" t="n">
@@ -9261,10 +9265,14 @@
       </c>
       <c r="H190" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I190" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I190" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/xTv7pw8qvp0</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="23.85" customHeight="1" s="32">
       <c r="A191" s="55" t="n">
@@ -9300,10 +9308,14 @@
       </c>
       <c r="H191" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I191" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I191" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Los9GAk7Jbk</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="15" customHeight="1" s="32">
       <c r="A192" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9351,10 +9351,14 @@
       </c>
       <c r="H192" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I192" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I192" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/gDTIpqKH7EA</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1" s="32">
       <c r="A193" s="55" t="n">
@@ -9390,10 +9394,14 @@
       </c>
       <c r="H193" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I193" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I193" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/bexuBFzPa4A</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="23.85" customHeight="1" s="32">
       <c r="A194" s="55" t="n">
@@ -9429,10 +9437,14 @@
       </c>
       <c r="H194" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I194" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I194" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/RWFrroKB0Hc</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1" s="32">
       <c r="A195" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9480,10 +9480,14 @@
       </c>
       <c r="H195" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I195" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I195" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8gZNrOCkoP4</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15" customHeight="1" s="32">
       <c r="A196" s="55" t="n">
@@ -9519,10 +9523,14 @@
       </c>
       <c r="H196" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I196" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I196" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/FEZNTv83jYQ</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="15" customHeight="1" s="32">
       <c r="A197" s="55" t="n">
@@ -9558,10 +9566,14 @@
       </c>
       <c r="H197" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I197" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I197" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7ivSlZ0tXtI</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="15" customHeight="1" s="32">
       <c r="A198" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9609,10 +9609,14 @@
       </c>
       <c r="H198" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I198" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I198" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/qKy7upQxQTU</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="15" customHeight="1" s="32">
       <c r="A199" s="55" t="n">
@@ -9648,10 +9652,14 @@
       </c>
       <c r="H199" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I199" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I199" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/bS7Np9VYY0g</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1" s="32">
       <c r="A200" s="55" t="n">
@@ -9687,10 +9695,14 @@
       </c>
       <c r="H200" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I200" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I200" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/v3MFjz50_wA</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="23.85" customHeight="1" s="32">
       <c r="A201" s="55" t="n">

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9738,10 +9738,14 @@
       </c>
       <c r="H201" s="55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I201" s="55" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I201" s="55" t="inlineStr">
+        <is>
+          <t>https://youtu.be/WriLkPPlosM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I301"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="31" min="1" max="1"/>
@@ -9744,6 +9744,3806 @@
       <c r="I201" s="55" t="inlineStr">
         <is>
           <t>https://youtu.be/WriLkPPlosM</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>29</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>I have teeth of metal but never chew; drag me through cheese and I'll shred it for you. What am I?</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>A grater</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>29</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Twist me down and I'll bite the cork, then pull it free without a fork. What am I?</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>A corkscrew</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>29</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>I roll back and forth but go nowhere at all, flattening dough till it's thin on the wall. What am I?</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>A rolling pin</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>30</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>I catch every drip and hold every soak, then wring myself dry at a squeeze or a choke. What am I?</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>A dishcloth</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>30</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>I keep your leftovers cold through the night, humming in darkness behind a shut light. What am I?</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>A refrigerator</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>30</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Spin my plate and I'll warm your meal, in seconds of hum you can hear but not feel. What am I?</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>A microwave</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>30</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>I press out your wrinkles with heat and with steam, then stand up on end when I've finished the seam. What am I?</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>An iron</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>30</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>I swallow the dust from under your feet, dragged room to room on a cord you repeat. What am I?</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>A vacuum</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>30</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>I mop up the floor from a bucket of grey, then hang up to dry at the end of the day. What am I?</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>A mop</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>30</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>I hug just one toe-to-heel each day, worn out in pairs then thrown away. What am I?</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>A sock</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>31</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>I circle your waist and I hold up your pants, tightened a notch after too many chances. What am I?</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>A belt</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>31</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>I ride on your back but I carry no weight of my own, filled up with books till your shoulders have grown. What am I?</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>A backpack</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>31</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>I hammer no nail yet I answer to swings; grip me to loosen the tightest of things. What am I?</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>A wrench</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>31</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>I turn and I turn but I travel nowhere, biting the wood till I'm buried in there. What am I?</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>A screw</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>31</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>I let a door swing and I let a lid lift; I fold in the middle, my one only gift. What am I?</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>A hinge</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>31</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>I coil up tight then I leap when set free, storing your push till you finally see. What am I?</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>A spring</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>31</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Six strings on my neck and a hole in my chest; strum me for songs at a campfire's request. What am I?</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>A guitar</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>32</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>I keep the beat with a tick and a sway, never a note but I show you the way. What am I?</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>A metronome</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>32</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>I spin round and round with a needle on top, and music pours out till you lift it to stop. What am I?</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>A record</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>32</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>I fall in the autumn, I'm green in the spring; I feed the whole tree yet I'm such a thin thing. What am I?</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>A leaf</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>32</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Buried in darkness, I wait for the rain, then split myself open to start it again. What am I?</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>A seed</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>32</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>I hoard my own water in a coat full of spears, standing in deserts for hundreds of years. What am I?</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>A cactus</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>32</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>I'm a mountain of water that falls off a cliff, roaring so loud you can feel the earth shift. What am I?</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>A waterfall</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>32</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Most of me hides where the cold currents flow; ships fear the tenth of me that doesn't show. What am I?</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>An iceberg</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>33</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>I hang from the gutter and grow with the cold, a dagger of water the winter has told. What am I?</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>An icicle</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>33</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>I'm a river of ice that crawls down the hill, carving the valley then leaving it still. What am I?</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>A glacier</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>33</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Closed I am woody, a fist full of seed; open in warmth I let the wind lead. What am I?</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>A pinecone</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>33</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>You bring me up close to bring far things near; the stars fill my eye when the night sky is clear. What am I?</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>A telescope</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>33</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>I make the invisible leap into view, blowing up specks that were too small for you. What am I?</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>A microscope</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>33</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>I split the white light into ribbons of hue, a triangle prism of red into blue. What am I?</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>A prism</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>33</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>I blast off with fire and I climb past the sky, shedding my stages the higher I fly. What am I?</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>A rocket</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>34</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>I circle the earth without touching the ground, bouncing your signals back safe and sound. What am I?</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>A satellite</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>34</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>I trail a bright tail as I swing past the sun, then vanish for lifetimes when my visit is done. What am I?</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>A comet</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>34</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>I dive without gills and I sail without wind, hiding in silence with sonar to find. What am I?</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>A submarine</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>34</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>I lift you in floors without climbing a stair, a box on a cable that carries you there. What am I?</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>An elevator</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>34</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>I bloom in the wind on a string you hold tight, tugging to climb to a paper-thin height. What am I?</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>A kite</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>34</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>I catch all the wind so a boat can move on; without me the sailor's swift journey is gone. What am I?</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>A sail</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>34</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Red, amber, green — I command every street, and cars hold their breath till my green says proceed. What am I?</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>A traffic light</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>35</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>I mark where you'll type with a blink and a bar, waiting on screen wherever you are. What am I?</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>A cursor</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>35</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Put a pound in my front and a topic behind, and suddenly thousands of posts you can find. What am I?</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>A hashtag</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>35</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>I'm the tiniest square that a screen can display; a million of me make the picture okay. What am I?</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>A pixel</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>35</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>I guard your machine from the traffic outside, deciding what enters and what is denied. What am I?</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>A firewall</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>35</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>A site drops me quietly to help it recall who you are on return, though I'm not sweet at all. What am I?</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>A cookie</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>35</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Blue and underlined, I whisk you away; one click and a whole other page is in play. What am I?</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>A hyperlink</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>35</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>I read a striped forehead of black and of white, and beep out a price at the checkout tonight. What am I?</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>A barcode</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>36</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>A camera that watches wherever you roam online, I show your own face on a call that's on time. What am I?</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>A webcam</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>36</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>I sit in a bowl of my own quiet steam, then poured into cups I'm the color of dream. Bag me or leaf me, I turn water to brew. What am I?</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>36</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>I circle your wrist and I count out your run, buzzing your steps till the walking is done. What am I?</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>A fitness tracker</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>36</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>I remember your logins, your cards, and your keys, locked in one vault that you open with ease. What am I?</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>A password manager</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>36</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>I keep a whole book in a slab you can hold, thousands of pages but nothing to fold. What am I?</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>An e-reader</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>36</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>I stand at the door with an eye and a chime, showing your porch on your phone anytime. What am I?</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>A doorbell camera</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>36</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>You speak and I listen from cross the whole room, dimming the lights or predicting the gloom. What am I?</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>A smart speaker</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>37</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>I am not a lie, but I'm not quite the truth; a story you tell to a gullible youth. Half-real, I grow with each telling anew. What am I?</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>An exaggeration</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>37</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>I count myself down till I hit at zero, then buzz or explode as the clock's little hero. What am I?</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>A countdown</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>37</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>I am the line where the sea meets the sky, always ahead, though you'll never draw nigh. What am I?</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>The horizon</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>37</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>I'm the promise of doing before it's too late; miss me and everyone circles the date. What am I?</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>A deadline</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>37</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>I am dropped in a box or I'm tapped on a screen; count all of me up and I crown a new queen or king. What am I?</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>A vote</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>37</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>I repeat what you did without asking you twice, hard to break loose and not always nice. What am I?</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>A habit</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>37</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>I prove you were elsewhere when trouble occurred, a story with witnesses, checked word for word. What am I?</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>An alibi</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>38</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>I'm the space you leave blank between word and word, without me a sentence would sound quite absurd. What am I?</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>A space</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>38</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>The more of me you take, the more you leave behind; I follow you walking but I'm not far behind. What am I?</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>A footstep</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>38</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>I have hands but no fingers, a face but no eyes; I run all day long but I stay the same size. What am I?</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>A clock</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>38</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>I chime on the hour with a swing and a weight, a grandfather standing that's never once late. What am I?</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>A pendulum clock</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>38</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>I have keys but no locks, space but no room; you enter me daily but I'm not a tomb. What am I?</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>A keyboard</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>38</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>I'm gold in the morning and cold in the night; I feed the whole world but I'm blinding to sight. What am I?</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>The sun</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>38</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>I wax and I wane and I borrow my light; I pull at the tides every single night. What am I?</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>The moon</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>39</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>I fall without hurting, I break without sound; I paint the whole town without touching the ground. What am I?</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Snow</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>39</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>You throw away my outside and cook my inside, then eat my outside and throw my inside. What am I?</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Corn on the cob</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>39</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>I have a ring for each year that I've grown, counted in circles once I've been thrown. What am I?</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>A tree trunk</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>39</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>I'm light as a feather, yet the strongest can't hold me for much more than a minute or so. What am I?</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>A breath</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>39</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Feed me and I grow tall and bright; give me a drink and I die in the night. What am I?</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>A fire</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>39</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>I'm the fifth if you letter my days of the week; find me in 'time' but in 'clock' I don't speak. What am I?</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>The letter T</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Wordplay</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>39</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>I'm easy to get into but hard to get out; the deeper you're in me, the more you'll dig about. What am I?</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Trouble</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>40</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Forwards I'm heavy, but backwards I'm not; read me both ways for the trick that I've got. What am I?</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>The word 'ton'</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Wordplay</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>40</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Give me food and I live; give me water and I die. Orange and flickering, I dance in the sky. What am I?</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>A flame</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>40</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>I ring without a mouth and run without a leg; a chime in your pocket you answer or beg. What am I?</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>A phone</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>40</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>I sit between two players and settle each fight, awarding the point with a whistle so bright. What am I?</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>A referee</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>40</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>I have a neck and a body but no arms at all; fill me with flowers to stand tall and proud. What am I?</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>A vase</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>40</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>I carry your voice to a friend far away, folded and stamped for the mail-carrier's tray. What am I?</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>A letter</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>40</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>I keep perfect time without gears or a spring; I follow the sun as it circles to bring my shadow around like a slow-moving thing. What am I?</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>A sundial</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>41</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>I flip your pancakes with a slide and a lift, wide and flat is my one only gift. What am I?</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>A spatula</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>41</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>I scoop out the soup with a deep little bowl on a long metal arm. What am I?</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>A ladle</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>41</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>I sense the room's warmth and I argue with it, turning the heat up or down bit by bit. What am I?</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>A thermostat</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>41</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>A doctor puts me in her ears to hear the drum of a beating so near. What am I?</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>A stethoscope</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>41</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>I bite once with a needle so thin, pushing the medicine under your skin. What am I?</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>A syringe</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>41</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>I wrap up a cut and I soak up the sore, sticking to skin till you need me no more. What am I?</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>A bandage</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>41</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>I lend you a leg when your own one is broken, tucked under your arm as a healing token. What am I?</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>A crutch</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>42</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Four wheels and a plank, I roll under your feet; kick once and I carry you down the whole street. What am I?</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>A skateboard</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>42</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>I'm a staircase that moves so your feet needn't climb; step on and I carry you up every time. What am I?</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>An escalator</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>42</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>I spin one at a time to let the crowd through, counting each body that passes on cue. What am I?</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>A turnstile</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>42</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>I bend like a horn but I sing like a reed; press down my keys for the jazz that you need. What am I?</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>A saxophone</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>42</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Cup me in your hands and breathe in and out; I hum out a blues with a bend and a shout. What am I?</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>A harmonica</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>42</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Strike my wooden bars with a mallet or two, and a ladder of notes comes ringing to you. What am I?</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>A xylophone</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>42</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Shake me or slap me, I jingle and ring, a circle of bells is the music I bring. What am I?</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>A tambourine</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>43</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Three valves and a bell, I blare loud and bright; press me for fanfares that carry for miles. What am I?</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>A trumpet</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>43</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Yellow when young, then I turn my head grey; blow on my seeds and they scatter away. What am I?</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>A dandelion</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>43</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Hold me to your ear on the sand by the sea, and the sound of the ocean is captured in me. What am I?</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>A seashell</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>43</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>I spin the water down into a swallowing throat, dragging under whatever won't stay afloat. What am I?</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>A whirlpool</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>43</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>I burst from the ground in a fountain of steam, boiling and timed like the earth's own dream. What am I?</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>A geyser</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>43</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>I twist from the sky in a funnel of wind, flinging up houses wherever I've been. What am I?</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>A tornado</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9748,3800 +9748,3815 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
+      <c r="A202" s="31" t="n">
         <v>201</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C202" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D202" s="31" t="inlineStr">
         <is>
           <t>I have teeth of metal but never chew; drag me through cheese and I'll shred it for you. What am I?</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E202" s="31" t="inlineStr">
         <is>
           <t>A grater</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F202" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G202" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H202" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I202" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/vA7qWsa0aG8</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
+      <c r="A203" s="31" t="n">
         <v>202</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C203" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" s="31" t="inlineStr">
         <is>
           <t>Twist me down and I'll bite the cork, then pull it free without a fork. What am I?</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E203" s="31" t="inlineStr">
         <is>
           <t>A corkscrew</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F203" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G203" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H203" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I203" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YuXh1pH30T4</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
+      <c r="A204" s="31" t="n">
         <v>203</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B204" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C204" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D204" s="31" t="inlineStr">
         <is>
           <t>I roll back and forth but go nowhere at all, flattening dough till it's thin on the wall. What am I?</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E204" s="31" t="inlineStr">
         <is>
           <t>A rolling pin</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F204" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G204" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H204" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>https://youtu.be/MTHkkCmgI30</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
+      <c r="A205" s="31" t="n">
         <v>204</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B205" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C205" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D205" s="31" t="inlineStr">
         <is>
           <t>I catch every drip and hold every soak, then wring myself dry at a squeeze or a choke. What am I?</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E205" s="31" t="inlineStr">
         <is>
           <t>A dishcloth</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F205" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G205" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H205" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206" s="31" t="n">
         <v>205</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B206" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C206" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D206" s="31" t="inlineStr">
         <is>
           <t>I keep your leftovers cold through the night, humming in darkness behind a shut light. What am I?</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E206" s="31" t="inlineStr">
         <is>
           <t>A refrigerator</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F206" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G206" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H206" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
+      <c r="A207" s="31" t="n">
         <v>206</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B207" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C207" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D207" s="31" t="inlineStr">
         <is>
           <t>Spin my plate and I'll warm your meal, in seconds of hum you can hear but not feel. What am I?</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E207" s="31" t="inlineStr">
         <is>
           <t>A microwave</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F207" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G207" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H207" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
+      <c r="A208" s="31" t="n">
         <v>207</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B208" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C208" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D208" s="31" t="inlineStr">
         <is>
           <t>I press out your wrinkles with heat and with steam, then stand up on end when I've finished the seam. What am I?</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E208" s="31" t="inlineStr">
         <is>
           <t>An iron</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F208" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G208" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H208" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
+      <c r="A209" s="31" t="n">
         <v>208</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B209" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C209" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D209" s="31" t="inlineStr">
         <is>
           <t>I swallow the dust from under your feet, dragged room to room on a cord you repeat. What am I?</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E209" s="31" t="inlineStr">
         <is>
           <t>A vacuum</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F209" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G209" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H209" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210" s="31" t="n">
         <v>209</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B210" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C210" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D210" s="31" t="inlineStr">
         <is>
           <t>I mop up the floor from a bucket of grey, then hang up to dry at the end of the day. What am I?</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E210" s="31" t="inlineStr">
         <is>
           <t>A mop</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F210" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G210" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H210" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
+      <c r="A211" s="31" t="n">
         <v>210</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B211" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C211" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D211" s="31" t="inlineStr">
         <is>
           <t>I hug just one toe-to-heel each day, worn out in pairs then thrown away. What am I?</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E211" s="31" t="inlineStr">
         <is>
           <t>A sock</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F211" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G211" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H211" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212" s="31" t="n">
         <v>211</v>
       </c>
-      <c r="B212" t="n">
+      <c r="B212" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C212" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D212" s="31" t="inlineStr">
         <is>
           <t>I circle your waist and I hold up your pants, tightened a notch after too many chances. What am I?</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E212" s="31" t="inlineStr">
         <is>
           <t>A belt</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F212" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G212" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="H212" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
+      <c r="A213" s="31" t="n">
         <v>212</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B213" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C213" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D213" s="31" t="inlineStr">
         <is>
           <t>I ride on your back but I carry no weight of my own, filled up with books till your shoulders have grown. What am I?</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E213" s="31" t="inlineStr">
         <is>
           <t>A backpack</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F213" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G213" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
+      <c r="H213" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
+      <c r="A214" s="31" t="n">
         <v>213</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C214" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D214" s="31" t="inlineStr">
         <is>
           <t>I hammer no nail yet I answer to swings; grip me to loosen the tightest of things. What am I?</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E214" s="31" t="inlineStr">
         <is>
           <t>A wrench</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F214" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="G214" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
+      <c r="H214" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
+      <c r="A215" s="31" t="n">
         <v>214</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B215" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C215" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" s="31" t="inlineStr">
         <is>
           <t>I turn and I turn but I travel nowhere, biting the wood till I'm buried in there. What am I?</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E215" s="31" t="inlineStr">
         <is>
           <t>A screw</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F215" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G215" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
+      <c r="H215" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
+      <c r="A216" s="31" t="n">
         <v>215</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B216" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C216" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D216" s="31" t="inlineStr">
         <is>
           <t>I let a door swing and I let a lid lift; I fold in the middle, my one only gift. What am I?</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E216" s="31" t="inlineStr">
         <is>
           <t>A hinge</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F216" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G216" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
+      <c r="H216" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
+      <c r="A217" s="31" t="n">
         <v>216</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B217" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C217" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" s="31" t="inlineStr">
         <is>
           <t>I coil up tight then I leap when set free, storing your push till you finally see. What am I?</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E217" s="31" t="inlineStr">
         <is>
           <t>A spring</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F217" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G217" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H217" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
+      <c r="A218" s="31" t="n">
         <v>217</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B218" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C218" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" s="31" t="inlineStr">
         <is>
           <t>Six strings on my neck and a hole in my chest; strum me for songs at a campfire's request. What am I?</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E218" s="31" t="inlineStr">
         <is>
           <t>A guitar</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F218" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G218" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="H218" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="n">
+      <c r="A219" s="31" t="n">
         <v>218</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B219" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C219" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="31" t="inlineStr">
         <is>
           <t>I keep the beat with a tick and a sway, never a note but I show you the way. What am I?</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E219" s="31" t="inlineStr">
         <is>
           <t>A metronome</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F219" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G219" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H219" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
+      <c r="A220" s="31" t="n">
         <v>219</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B220" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="31" t="inlineStr">
         <is>
           <t>I spin round and round with a needle on top, and music pours out till you lift it to stop. What am I?</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E220" s="31" t="inlineStr">
         <is>
           <t>A record</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F220" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G220" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H220" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
+      <c r="A221" s="31" t="n">
         <v>220</v>
       </c>
-      <c r="B221" t="n">
+      <c r="B221" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="31" t="inlineStr">
         <is>
           <t>I fall in the autumn, I'm green in the spring; I feed the whole tree yet I'm such a thin thing. What am I?</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E221" s="31" t="inlineStr">
         <is>
           <t>A leaf</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F221" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G221" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H221" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
+      <c r="A222" s="31" t="n">
         <v>221</v>
       </c>
-      <c r="B222" t="n">
+      <c r="B222" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C222" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D222" s="31" t="inlineStr">
         <is>
           <t>Buried in darkness, I wait for the rain, then split myself open to start it again. What am I?</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E222" s="31" t="inlineStr">
         <is>
           <t>A seed</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F222" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G222" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="H222" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
+      <c r="A223" s="31" t="n">
         <v>222</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B223" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C223" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D223" s="31" t="inlineStr">
         <is>
           <t>I hoard my own water in a coat full of spears, standing in deserts for hundreds of years. What am I?</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E223" s="31" t="inlineStr">
         <is>
           <t>A cactus</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F223" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G223" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H223" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
+      <c r="A224" s="31" t="n">
         <v>223</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B224" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C224" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D224" s="31" t="inlineStr">
         <is>
           <t>I'm a mountain of water that falls off a cliff, roaring so loud you can feel the earth shift. What am I?</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E224" s="31" t="inlineStr">
         <is>
           <t>A waterfall</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F224" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G224" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
+      <c r="H224" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
+      <c r="A225" s="31" t="n">
         <v>224</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B225" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C225" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D225" s="31" t="inlineStr">
         <is>
           <t>Most of me hides where the cold currents flow; ships fear the tenth of me that doesn't show. What am I?</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E225" s="31" t="inlineStr">
         <is>
           <t>An iceberg</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F225" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G225" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="H225" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
+      <c r="A226" s="31" t="n">
         <v>225</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B226" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C226" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D226" s="31" t="inlineStr">
         <is>
           <t>I hang from the gutter and grow with the cold, a dagger of water the winter has told. What am I?</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E226" s="31" t="inlineStr">
         <is>
           <t>An icicle</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F226" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G226" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
+      <c r="H226" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
+      <c r="A227" s="31" t="n">
         <v>226</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C227" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D227" s="31" t="inlineStr">
         <is>
           <t>I'm a river of ice that crawls down the hill, carving the valley then leaving it still. What am I?</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E227" s="31" t="inlineStr">
         <is>
           <t>A glacier</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F227" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G227" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
+      <c r="H227" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
+      <c r="A228" s="31" t="n">
         <v>227</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B228" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C228" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D228" s="31" t="inlineStr">
         <is>
           <t>Closed I am woody, a fist full of seed; open in warmth I let the wind lead. What am I?</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E228" s="31" t="inlineStr">
         <is>
           <t>A pinecone</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F228" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G228" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
+      <c r="H228" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
+      <c r="A229" s="31" t="n">
         <v>228</v>
       </c>
-      <c r="B229" t="n">
+      <c r="B229" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C229" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D229" s="31" t="inlineStr">
         <is>
           <t>You bring me up close to bring far things near; the stars fill my eye when the night sky is clear. What am I?</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E229" s="31" t="inlineStr">
         <is>
           <t>A telescope</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F229" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G229" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
+      <c r="H229" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
+      <c r="A230" s="31" t="n">
         <v>229</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C230" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D230" s="31" t="inlineStr">
         <is>
           <t>I make the invisible leap into view, blowing up specks that were too small for you. What am I?</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E230" s="31" t="inlineStr">
         <is>
           <t>A microscope</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="F230" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G230" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="H230" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
+      <c r="A231" s="31" t="n">
         <v>230</v>
       </c>
-      <c r="B231" t="n">
+      <c r="B231" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C231" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D231" s="31" t="inlineStr">
         <is>
           <t>I split the white light into ribbons of hue, a triangle prism of red into blue. What am I?</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E231" s="31" t="inlineStr">
         <is>
           <t>A prism</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F231" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G231" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
+      <c r="H231" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
+      <c r="A232" s="31" t="n">
         <v>231</v>
       </c>
-      <c r="B232" t="n">
+      <c r="B232" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C232" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D232" s="31" t="inlineStr">
         <is>
           <t>I blast off with fire and I climb past the sky, shedding my stages the higher I fly. What am I?</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E232" s="31" t="inlineStr">
         <is>
           <t>A rocket</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F232" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G232" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H232" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
+      <c r="A233" s="31" t="n">
         <v>232</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B233" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C233" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D233" s="31" t="inlineStr">
         <is>
           <t>I circle the earth without touching the ground, bouncing your signals back safe and sound. What am I?</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E233" s="31" t="inlineStr">
         <is>
           <t>A satellite</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F233" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G233" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
+      <c r="H233" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
+      <c r="A234" s="31" t="n">
         <v>233</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C234" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D234" s="31" t="inlineStr">
         <is>
           <t>I trail a bright tail as I swing past the sun, then vanish for lifetimes when my visit is done. What am I?</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E234" s="31" t="inlineStr">
         <is>
           <t>A comet</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F234" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G234" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
+      <c r="H234" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
+      <c r="A235" s="31" t="n">
         <v>234</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B235" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C235" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D235" s="31" t="inlineStr">
         <is>
           <t>I dive without gills and I sail without wind, hiding in silence with sonar to find. What am I?</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E235" s="31" t="inlineStr">
         <is>
           <t>A submarine</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F235" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G235" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
+      <c r="H235" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
+      <c r="A236" s="31" t="n">
         <v>235</v>
       </c>
-      <c r="B236" t="n">
+      <c r="B236" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C236" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D236" s="31" t="inlineStr">
         <is>
           <t>I lift you in floors without climbing a stair, a box on a cable that carries you there. What am I?</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E236" s="31" t="inlineStr">
         <is>
           <t>An elevator</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F236" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G236" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
+      <c r="H236" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="n">
+      <c r="A237" s="31" t="n">
         <v>236</v>
       </c>
-      <c r="B237" t="n">
+      <c r="B237" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C237" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D237" s="31" t="inlineStr">
         <is>
           <t>I bloom in the wind on a string you hold tight, tugging to climb to a paper-thin height. What am I?</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E237" s="31" t="inlineStr">
         <is>
           <t>A kite</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
+      <c r="F237" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G237" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
+      <c r="H237" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
+      <c r="A238" s="31" t="n">
         <v>237</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B238" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C238" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D238" s="31" t="inlineStr">
         <is>
           <t>I catch all the wind so a boat can move on; without me the sailor's swift journey is gone. What am I?</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E238" s="31" t="inlineStr">
         <is>
           <t>A sail</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
+      <c r="F238" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G238" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
+      <c r="H238" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="n">
+      <c r="A239" s="31" t="n">
         <v>238</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B239" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C239" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D239" s="31" t="inlineStr">
         <is>
           <t>Red, amber, green — I command every street, and cars hold their breath till my green says proceed. What am I?</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E239" s="31" t="inlineStr">
         <is>
           <t>A traffic light</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F239" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G239" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
+      <c r="H239" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="n">
+      <c r="A240" s="31" t="n">
         <v>239</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B240" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C240" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D240" s="31" t="inlineStr">
         <is>
           <t>I mark where you'll type with a blink and a bar, waiting on screen wherever you are. What am I?</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E240" s="31" t="inlineStr">
         <is>
           <t>A cursor</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
+      <c r="F240" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G240" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
+      <c r="H240" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
+      <c r="A241" s="31" t="n">
         <v>240</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B241" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C241" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D241" s="31" t="inlineStr">
         <is>
           <t>Put a pound in my front and a topic behind, and suddenly thousands of posts you can find. What am I?</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E241" s="31" t="inlineStr">
         <is>
           <t>A hashtag</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
+      <c r="F241" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G241" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
+      <c r="H241" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
+      <c r="A242" s="31" t="n">
         <v>241</v>
       </c>
-      <c r="B242" t="n">
+      <c r="B242" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C242" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D242" s="31" t="inlineStr">
         <is>
           <t>I'm the tiniest square that a screen can display; a million of me make the picture okay. What am I?</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E242" s="31" t="inlineStr">
         <is>
           <t>A pixel</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="F242" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
+      <c r="G242" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
+      <c r="H242" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
+      <c r="A243" s="31" t="n">
         <v>242</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B243" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C243" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D243" s="31" t="inlineStr">
         <is>
           <t>I guard your machine from the traffic outside, deciding what enters and what is denied. What am I?</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E243" s="31" t="inlineStr">
         <is>
           <t>A firewall</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="F243" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="G243" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
+      <c r="H243" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="n">
+      <c r="A244" s="31" t="n">
         <v>243</v>
       </c>
-      <c r="B244" t="n">
+      <c r="B244" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C244" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D244" s="31" t="inlineStr">
         <is>
           <t>A site drops me quietly to help it recall who you are on return, though I'm not sweet at all. What am I?</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E244" s="31" t="inlineStr">
         <is>
           <t>A cookie</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
+      <c r="F244" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
+      <c r="G244" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
+      <c r="H244" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
+      <c r="A245" s="31" t="n">
         <v>244</v>
       </c>
-      <c r="B245" t="n">
+      <c r="B245" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C245" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D245" s="31" t="inlineStr">
         <is>
           <t>Blue and underlined, I whisk you away; one click and a whole other page is in play. What am I?</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E245" s="31" t="inlineStr">
         <is>
           <t>A hyperlink</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
+      <c r="F245" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
+      <c r="G245" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
+      <c r="H245" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
+      <c r="A246" s="31" t="n">
         <v>245</v>
       </c>
-      <c r="B246" t="n">
+      <c r="B246" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C246" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D246" s="31" t="inlineStr">
         <is>
           <t>I read a striped forehead of black and of white, and beep out a price at the checkout tonight. What am I?</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E246" s="31" t="inlineStr">
         <is>
           <t>A barcode</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F246" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G246" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
+      <c r="H246" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
+      <c r="A247" s="31" t="n">
         <v>246</v>
       </c>
-      <c r="B247" t="n">
+      <c r="B247" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C247" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D247" s="31" t="inlineStr">
         <is>
           <t>A camera that watches wherever you roam online, I show your own face on a call that's on time. What am I?</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E247" s="31" t="inlineStr">
         <is>
           <t>A webcam</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
+      <c r="F247" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G247" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
+      <c r="H247" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="n">
+      <c r="A248" s="31" t="n">
         <v>247</v>
       </c>
-      <c r="B248" t="n">
+      <c r="B248" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C248" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D248" s="31" t="inlineStr">
         <is>
           <t>I sit in a bowl of my own quiet steam, then poured into cups I'm the color of dream. Bag me or leaf me, I turn water to brew. What am I?</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E248" s="31" t="inlineStr">
         <is>
           <t>Tea</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
+      <c r="F248" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
+      <c r="G248" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H248" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
+      <c r="A249" s="31" t="n">
         <v>248</v>
       </c>
-      <c r="B249" t="n">
+      <c r="B249" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D249" s="31" t="inlineStr">
         <is>
           <t>I circle your wrist and I count out your run, buzzing your steps till the walking is done. What am I?</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E249" s="31" t="inlineStr">
         <is>
           <t>A fitness tracker</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="F249" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
+      <c r="G249" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
+      <c r="H249" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="n">
+      <c r="A250" s="31" t="n">
         <v>249</v>
       </c>
-      <c r="B250" t="n">
+      <c r="B250" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D250" s="31" t="inlineStr">
         <is>
           <t>I remember your logins, your cards, and your keys, locked in one vault that you open with ease. What am I?</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E250" s="31" t="inlineStr">
         <is>
           <t>A password manager</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
+      <c r="F250" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G250" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
+      <c r="H250" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
+      <c r="A251" s="31" t="n">
         <v>250</v>
       </c>
-      <c r="B251" t="n">
+      <c r="B251" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C251" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D251" s="31" t="inlineStr">
         <is>
           <t>I keep a whole book in a slab you can hold, thousands of pages but nothing to fold. What am I?</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E251" s="31" t="inlineStr">
         <is>
           <t>An e-reader</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
+      <c r="F251" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
+      <c r="G251" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
+      <c r="H251" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="n">
+      <c r="A252" s="31" t="n">
         <v>251</v>
       </c>
-      <c r="B252" t="n">
+      <c r="B252" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C252" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D252" s="31" t="inlineStr">
         <is>
           <t>I stand at the door with an eye and a chime, showing your porch on your phone anytime. What am I?</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E252" s="31" t="inlineStr">
         <is>
           <t>A doorbell camera</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
+      <c r="F252" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
+      <c r="G252" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
+      <c r="H252" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
+      <c r="A253" s="31" t="n">
         <v>252</v>
       </c>
-      <c r="B253" t="n">
+      <c r="B253" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D253" s="31" t="inlineStr">
         <is>
           <t>You speak and I listen from cross the whole room, dimming the lights or predicting the gloom. What am I?</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E253" s="31" t="inlineStr">
         <is>
           <t>A smart speaker</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
+      <c r="F253" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
+      <c r="G253" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
+      <c r="H253" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
+      <c r="A254" s="31" t="n">
         <v>253</v>
       </c>
-      <c r="B254" t="n">
+      <c r="B254" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C254" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D254" s="31" t="inlineStr">
         <is>
           <t>I am not a lie, but I'm not quite the truth; a story you tell to a gullible youth. Half-real, I grow with each telling anew. What am I?</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E254" s="31" t="inlineStr">
         <is>
           <t>An exaggeration</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
+      <c r="F254" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
+      <c r="G254" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H254" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
+      <c r="A255" s="31" t="n">
         <v>254</v>
       </c>
-      <c r="B255" t="n">
+      <c r="B255" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C255" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D255" s="31" t="inlineStr">
         <is>
           <t>I count myself down till I hit at zero, then buzz or explode as the clock's little hero. What am I?</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E255" s="31" t="inlineStr">
         <is>
           <t>A countdown</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F255" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G255" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
+      <c r="H255" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="n">
+      <c r="A256" s="31" t="n">
         <v>255</v>
       </c>
-      <c r="B256" t="n">
+      <c r="B256" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C256" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D256" s="31" t="inlineStr">
         <is>
           <t>I am the line where the sea meets the sky, always ahead, though you'll never draw nigh. What am I?</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E256" s="31" t="inlineStr">
         <is>
           <t>The horizon</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
+      <c r="F256" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
+      <c r="G256" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
+      <c r="H256" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="n">
+      <c r="A257" s="31" t="n">
         <v>256</v>
       </c>
-      <c r="B257" t="n">
+      <c r="B257" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C257" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D257" s="31" t="inlineStr">
         <is>
           <t>I'm the promise of doing before it's too late; miss me and everyone circles the date. What am I?</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E257" s="31" t="inlineStr">
         <is>
           <t>A deadline</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
+      <c r="F257" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G257" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
+      <c r="H257" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="n">
+      <c r="A258" s="31" t="n">
         <v>257</v>
       </c>
-      <c r="B258" t="n">
+      <c r="B258" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C258" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D258" s="31" t="inlineStr">
         <is>
           <t>I am dropped in a box or I'm tapped on a screen; count all of me up and I crown a new queen or king. What am I?</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E258" s="31" t="inlineStr">
         <is>
           <t>A vote</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
+      <c r="F258" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G258" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
+      <c r="H258" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="n">
+      <c r="A259" s="31" t="n">
         <v>258</v>
       </c>
-      <c r="B259" t="n">
+      <c r="B259" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C259" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D259" s="31" t="inlineStr">
         <is>
           <t>I repeat what you did without asking you twice, hard to break loose and not always nice. What am I?</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E259" s="31" t="inlineStr">
         <is>
           <t>A habit</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
+      <c r="F259" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G259" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H259" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="n">
+      <c r="A260" s="31" t="n">
         <v>259</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B260" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C260" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D260" s="31" t="inlineStr">
         <is>
           <t>I prove you were elsewhere when trouble occurred, a story with witnesses, checked word for word. What am I?</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E260" s="31" t="inlineStr">
         <is>
           <t>An alibi</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F260" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G260" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H260" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="n">
+      <c r="A261" s="31" t="n">
         <v>260</v>
       </c>
-      <c r="B261" t="n">
+      <c r="B261" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C261" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D261" s="31" t="inlineStr">
         <is>
           <t>I'm the space you leave blank between word and word, without me a sentence would sound quite absurd. What am I?</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E261" s="31" t="inlineStr">
         <is>
           <t>A space</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
+      <c r="F261" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G261" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H261" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="n">
+      <c r="A262" s="31" t="n">
         <v>261</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C262" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D262" s="31" t="inlineStr">
         <is>
           <t>The more of me you take, the more you leave behind; I follow you walking but I'm not far behind. What am I?</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" s="31" t="inlineStr">
         <is>
           <t>A footstep</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F262" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G262" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H262" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
+      <c r="A263" s="31" t="n">
         <v>262</v>
       </c>
-      <c r="B263" t="n">
+      <c r="B263" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C263" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D263" s="31" t="inlineStr">
         <is>
           <t>I have hands but no fingers, a face but no eyes; I run all day long but I stay the same size. What am I?</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E263" s="31" t="inlineStr">
         <is>
           <t>A clock</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F263" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G263" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H263" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="n">
+      <c r="A264" s="31" t="n">
         <v>263</v>
       </c>
-      <c r="B264" t="n">
+      <c r="B264" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C264" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D264" s="31" t="inlineStr">
         <is>
           <t>I chime on the hour with a swing and a weight, a grandfather standing that's never once late. What am I?</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E264" s="31" t="inlineStr">
         <is>
           <t>A pendulum clock</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F264" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G264" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H264" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="n">
+      <c r="A265" s="31" t="n">
         <v>264</v>
       </c>
-      <c r="B265" t="n">
+      <c r="B265" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C265" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D265" s="31" t="inlineStr">
         <is>
           <t>I have keys but no locks, space but no room; you enter me daily but I'm not a tomb. What am I?</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E265" s="31" t="inlineStr">
         <is>
           <t>A keyboard</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
+      <c r="F265" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="G265" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
+      <c r="H265" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="n">
+      <c r="A266" s="31" t="n">
         <v>265</v>
       </c>
-      <c r="B266" t="n">
+      <c r="B266" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C266" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D266" s="31" t="inlineStr">
         <is>
           <t>I'm gold in the morning and cold in the night; I feed the whole world but I'm blinding to sight. What am I?</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E266" s="31" t="inlineStr">
         <is>
           <t>The sun</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F266" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G266" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H266" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="n">
+      <c r="A267" s="31" t="n">
         <v>266</v>
       </c>
-      <c r="B267" t="n">
+      <c r="B267" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="C267" t="inlineStr">
+      <c r="C267" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D267" s="31" t="inlineStr">
         <is>
           <t>I wax and I wane and I borrow my light; I pull at the tides every single night. What am I?</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E267" s="31" t="inlineStr">
         <is>
           <t>The moon</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F267" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G267" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
+      <c r="H267" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="n">
+      <c r="A268" s="31" t="n">
         <v>267</v>
       </c>
-      <c r="B268" t="n">
+      <c r="B268" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="C268" t="inlineStr">
+      <c r="C268" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D268" s="31" t="inlineStr">
         <is>
           <t>I fall without hurting, I break without sound; I paint the whole town without touching the ground. What am I?</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="E268" s="31" t="inlineStr">
         <is>
           <t>Snow</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
+      <c r="F268" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
+      <c r="G268" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
+      <c r="H268" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="n">
+      <c r="A269" s="31" t="n">
         <v>268</v>
       </c>
-      <c r="B269" t="n">
+      <c r="B269" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C269" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D269" s="31" t="inlineStr">
         <is>
           <t>You throw away my outside and cook my inside, then eat my outside and throw my inside. What am I?</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E269" s="31" t="inlineStr">
         <is>
           <t>Corn on the cob</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
+      <c r="F269" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="G269" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
+      <c r="H269" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="n">
+      <c r="A270" s="31" t="n">
         <v>269</v>
       </c>
-      <c r="B270" t="n">
+      <c r="B270" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C270" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D270" s="31" t="inlineStr">
         <is>
           <t>I have a ring for each year that I've grown, counted in circles once I've been thrown. What am I?</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E270" s="31" t="inlineStr">
         <is>
           <t>A tree trunk</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
+      <c r="F270" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
+      <c r="G270" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
+      <c r="H270" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="n">
+      <c r="A271" s="31" t="n">
         <v>270</v>
       </c>
-      <c r="B271" t="n">
+      <c r="B271" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C271" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D271" s="31" t="inlineStr">
         <is>
           <t>I'm light as a feather, yet the strongest can't hold me for much more than a minute or so. What am I?</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E271" s="31" t="inlineStr">
         <is>
           <t>A breath</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F271" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="G271" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="H271" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="n">
+      <c r="A272" s="31" t="n">
         <v>271</v>
       </c>
-      <c r="B272" t="n">
+      <c r="B272" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C272" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D272" s="31" t="inlineStr">
         <is>
           <t>Feed me and I grow tall and bright; give me a drink and I die in the night. What am I?</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="E272" s="31" t="inlineStr">
         <is>
           <t>A fire</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="F272" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G272" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
+      <c r="H272" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="n">
+      <c r="A273" s="31" t="n">
         <v>272</v>
       </c>
-      <c r="B273" t="n">
+      <c r="B273" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C273" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D273" s="31" t="inlineStr">
         <is>
           <t>I'm the fifth if you letter my days of the week; find me in 'time' but in 'clock' I don't speak. What am I?</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E273" s="31" t="inlineStr">
         <is>
           <t>The letter T</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F273" s="31" t="inlineStr">
         <is>
           <t>Wordplay</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G273" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
+      <c r="H273" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="n">
+      <c r="A274" s="31" t="n">
         <v>273</v>
       </c>
-      <c r="B274" t="n">
+      <c r="B274" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C274" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D274" s="31" t="inlineStr">
         <is>
           <t>I'm easy to get into but hard to get out; the deeper you're in me, the more you'll dig about. What am I?</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E274" s="31" t="inlineStr">
         <is>
           <t>Trouble</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F274" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
+      <c r="G274" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
+      <c r="H274" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="n">
+      <c r="A275" s="31" t="n">
         <v>274</v>
       </c>
-      <c r="B275" t="n">
+      <c r="B275" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C275" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D275" s="31" t="inlineStr">
         <is>
           <t>Forwards I'm heavy, but backwards I'm not; read me both ways for the trick that I've got. What am I?</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="E275" s="31" t="inlineStr">
         <is>
           <t>The word 'ton'</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
+      <c r="F275" s="31" t="inlineStr">
         <is>
           <t>Wordplay</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
+      <c r="G275" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
+      <c r="H275" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
+      <c r="A276" s="31" t="n">
         <v>275</v>
       </c>
-      <c r="B276" t="n">
+      <c r="B276" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C276" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D276" s="31" t="inlineStr">
         <is>
           <t>Give me food and I live; give me water and I die. Orange and flickering, I dance in the sky. What am I?</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
+      <c r="E276" s="31" t="inlineStr">
         <is>
           <t>A flame</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F276" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
+      <c r="G276" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
+      <c r="H276" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="n">
+      <c r="A277" s="31" t="n">
         <v>276</v>
       </c>
-      <c r="B277" t="n">
+      <c r="B277" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C277" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="D277" s="31" t="inlineStr">
         <is>
           <t>I ring without a mouth and run without a leg; a chime in your pocket you answer or beg. What am I?</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
+      <c r="E277" s="31" t="inlineStr">
         <is>
           <t>A phone</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
+      <c r="F277" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
+      <c r="G277" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
+      <c r="H277" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="n">
+      <c r="A278" s="31" t="n">
         <v>277</v>
       </c>
-      <c r="B278" t="n">
+      <c r="B278" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C278" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D278" s="31" t="inlineStr">
         <is>
           <t>I sit between two players and settle each fight, awarding the point with a whistle so bright. What am I?</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="E278" s="31" t="inlineStr">
         <is>
           <t>A referee</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
+      <c r="F278" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
+      <c r="G278" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
+      <c r="H278" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="n">
+      <c r="A279" s="31" t="n">
         <v>278</v>
       </c>
-      <c r="B279" t="n">
+      <c r="B279" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C279" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D279" s="31" t="inlineStr">
         <is>
           <t>I have a neck and a body but no arms at all; fill me with flowers to stand tall and proud. What am I?</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="E279" s="31" t="inlineStr">
         <is>
           <t>A vase</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
+      <c r="F279" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
+      <c r="G279" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
+      <c r="H279" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="n">
+      <c r="A280" s="31" t="n">
         <v>279</v>
       </c>
-      <c r="B280" t="n">
+      <c r="B280" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C280" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D280" s="31" t="inlineStr">
         <is>
           <t>I carry your voice to a friend far away, folded and stamped for the mail-carrier's tray. What am I?</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E280" s="31" t="inlineStr">
         <is>
           <t>A letter</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F280" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="G280" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
+      <c r="H280" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="n">
+      <c r="A281" s="31" t="n">
         <v>280</v>
       </c>
-      <c r="B281" t="n">
+      <c r="B281" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C281" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D281" s="31" t="inlineStr">
         <is>
           <t>I keep perfect time without gears or a spring; I follow the sun as it circles to bring my shadow around like a slow-moving thing. What am I?</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="E281" s="31" t="inlineStr">
         <is>
           <t>A sundial</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
+      <c r="F281" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
+      <c r="G281" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
+      <c r="H281" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="n">
+      <c r="A282" s="31" t="n">
         <v>281</v>
       </c>
-      <c r="B282" t="n">
+      <c r="B282" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="C282" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D282" s="31" t="inlineStr">
         <is>
           <t>I flip your pancakes with a slide and a lift, wide and flat is my one only gift. What am I?</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E282" s="31" t="inlineStr">
         <is>
           <t>A spatula</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
+      <c r="F282" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
+      <c r="G282" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
+      <c r="H282" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="n">
+      <c r="A283" s="31" t="n">
         <v>282</v>
       </c>
-      <c r="B283" t="n">
+      <c r="B283" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C283" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D283" s="31" t="inlineStr">
         <is>
           <t>I scoop out the soup with a deep little bowl on a long metal arm. What am I?</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E283" s="31" t="inlineStr">
         <is>
           <t>A ladle</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
+      <c r="F283" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
+      <c r="G283" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
+      <c r="H283" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="n">
+      <c r="A284" s="31" t="n">
         <v>283</v>
       </c>
-      <c r="B284" t="n">
+      <c r="B284" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C284" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D284" s="31" t="inlineStr">
         <is>
           <t>I sense the room's warmth and I argue with it, turning the heat up or down bit by bit. What am I?</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="E284" s="31" t="inlineStr">
         <is>
           <t>A thermostat</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
+      <c r="F284" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
+      <c r="G284" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
+      <c r="H284" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="n">
+      <c r="A285" s="31" t="n">
         <v>284</v>
       </c>
-      <c r="B285" t="n">
+      <c r="B285" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C285" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D285" s="31" t="inlineStr">
         <is>
           <t>A doctor puts me in her ears to hear the drum of a beating so near. What am I?</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E285" s="31" t="inlineStr">
         <is>
           <t>A stethoscope</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
+      <c r="F285" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
+      <c r="G285" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
+      <c r="H285" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="n">
+      <c r="A286" s="31" t="n">
         <v>285</v>
       </c>
-      <c r="B286" t="n">
+      <c r="B286" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C286" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D286" s="31" t="inlineStr">
         <is>
           <t>I bite once with a needle so thin, pushing the medicine under your skin. What am I?</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E286" s="31" t="inlineStr">
         <is>
           <t>A syringe</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
+      <c r="F286" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
+      <c r="G286" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
+      <c r="H286" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="n">
+      <c r="A287" s="31" t="n">
         <v>286</v>
       </c>
-      <c r="B287" t="n">
+      <c r="B287" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C287" t="inlineStr">
+      <c r="C287" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="D287" s="31" t="inlineStr">
         <is>
           <t>I wrap up a cut and I soak up the sore, sticking to skin till you need me no more. What am I?</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="E287" s="31" t="inlineStr">
         <is>
           <t>A bandage</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
+      <c r="F287" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
+      <c r="G287" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
+      <c r="H287" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="n">
+      <c r="A288" s="31" t="n">
         <v>287</v>
       </c>
-      <c r="B288" t="n">
+      <c r="B288" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C288" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D288" s="31" t="inlineStr">
         <is>
           <t>I lend you a leg when your own one is broken, tucked under your arm as a healing token. What am I?</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="E288" s="31" t="inlineStr">
         <is>
           <t>A crutch</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
+      <c r="F288" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
+      <c r="G288" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
+      <c r="H288" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="n">
+      <c r="A289" s="31" t="n">
         <v>288</v>
       </c>
-      <c r="B289" t="n">
+      <c r="B289" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="C289" t="inlineStr">
+      <c r="C289" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D289" s="31" t="inlineStr">
         <is>
           <t>Four wheels and a plank, I roll under your feet; kick once and I carry you down the whole street. What am I?</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
+      <c r="E289" s="31" t="inlineStr">
         <is>
           <t>A skateboard</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
+      <c r="F289" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
+      <c r="G289" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
+      <c r="H289" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="n">
+      <c r="A290" s="31" t="n">
         <v>289</v>
       </c>
-      <c r="B290" t="n">
+      <c r="B290" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="C290" t="inlineStr">
+      <c r="C290" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="D290" s="31" t="inlineStr">
         <is>
           <t>I'm a staircase that moves so your feet needn't climb; step on and I carry you up every time. What am I?</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
+      <c r="E290" s="31" t="inlineStr">
         <is>
           <t>An escalator</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
+      <c r="F290" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
+      <c r="G290" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
+      <c r="H290" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="n">
+      <c r="A291" s="31" t="n">
         <v>290</v>
       </c>
-      <c r="B291" t="n">
+      <c r="B291" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="C291" t="inlineStr">
+      <c r="C291" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr">
+      <c r="D291" s="31" t="inlineStr">
         <is>
           <t>I spin one at a time to let the crowd through, counting each body that passes on cue. What am I?</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
+      <c r="E291" s="31" t="inlineStr">
         <is>
           <t>A turnstile</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
+      <c r="F291" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
+      <c r="G291" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
+      <c r="H291" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="n">
+      <c r="A292" s="31" t="n">
         <v>291</v>
       </c>
-      <c r="B292" t="n">
+      <c r="B292" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="C292" t="inlineStr">
+      <c r="C292" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
+      <c r="D292" s="31" t="inlineStr">
         <is>
           <t>I bend like a horn but I sing like a reed; press down my keys for the jazz that you need. What am I?</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
+      <c r="E292" s="31" t="inlineStr">
         <is>
           <t>A saxophone</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
+      <c r="F292" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
+      <c r="G292" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
+      <c r="H292" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="n">
+      <c r="A293" s="31" t="n">
         <v>292</v>
       </c>
-      <c r="B293" t="n">
+      <c r="B293" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="C293" t="inlineStr">
+      <c r="C293" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr">
+      <c r="D293" s="31" t="inlineStr">
         <is>
           <t>Cup me in your hands and breathe in and out; I hum out a blues with a bend and a shout. What am I?</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
+      <c r="E293" s="31" t="inlineStr">
         <is>
           <t>A harmonica</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
+      <c r="F293" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
+      <c r="G293" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
+      <c r="H293" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="n">
+      <c r="A294" s="31" t="n">
         <v>293</v>
       </c>
-      <c r="B294" t="n">
+      <c r="B294" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="C294" t="inlineStr">
+      <c r="C294" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
+      <c r="D294" s="31" t="inlineStr">
         <is>
           <t>Strike my wooden bars with a mallet or two, and a ladder of notes comes ringing to you. What am I?</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
+      <c r="E294" s="31" t="inlineStr">
         <is>
           <t>A xylophone</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
+      <c r="F294" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
+      <c r="G294" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
+      <c r="H294" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="n">
+      <c r="A295" s="31" t="n">
         <v>294</v>
       </c>
-      <c r="B295" t="n">
+      <c r="B295" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="C295" t="inlineStr">
+      <c r="C295" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr">
+      <c r="D295" s="31" t="inlineStr">
         <is>
           <t>Shake me or slap me, I jingle and ring, a circle of bells is the music I bring. What am I?</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
+      <c r="E295" s="31" t="inlineStr">
         <is>
           <t>A tambourine</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
+      <c r="F295" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
+      <c r="G295" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
+      <c r="H295" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="n">
+      <c r="A296" s="31" t="n">
         <v>295</v>
       </c>
-      <c r="B296" t="n">
+      <c r="B296" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C296" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="D296" s="31" t="inlineStr">
         <is>
           <t>Three valves and a bell, I blare loud and bright; press me for fanfares that carry for miles. What am I?</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
+      <c r="E296" s="31" t="inlineStr">
         <is>
           <t>A trumpet</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
+      <c r="F296" s="31" t="inlineStr">
         <is>
           <t>Object</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
+      <c r="G296" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
+      <c r="H296" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="n">
+      <c r="A297" s="31" t="n">
         <v>296</v>
       </c>
-      <c r="B297" t="n">
+      <c r="B297" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C297" t="inlineStr">
+      <c r="C297" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="D297" s="31" t="inlineStr">
         <is>
           <t>Yellow when young, then I turn my head grey; blow on my seeds and they scatter away. What am I?</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
+      <c r="E297" s="31" t="inlineStr">
         <is>
           <t>A dandelion</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
+      <c r="F297" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
+      <c r="G297" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
+      <c r="H297" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="n">
+      <c r="A298" s="31" t="n">
         <v>297</v>
       </c>
-      <c r="B298" t="n">
+      <c r="B298" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C298" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="D298" s="31" t="inlineStr">
         <is>
           <t>Hold me to your ear on the sand by the sea, and the sound of the ocean is captured in me. What am I?</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
+      <c r="E298" s="31" t="inlineStr">
         <is>
           <t>A seashell</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
+      <c r="F298" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
+      <c r="G298" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
+      <c r="H298" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="n">
+      <c r="A299" s="31" t="n">
         <v>298</v>
       </c>
-      <c r="B299" t="n">
+      <c r="B299" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C299" t="inlineStr">
+      <c r="C299" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
+      <c r="D299" s="31" t="inlineStr">
         <is>
           <t>I spin the water down into a swallowing throat, dragging under whatever won't stay afloat. What am I?</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
+      <c r="E299" s="31" t="inlineStr">
         <is>
           <t>A whirlpool</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
+      <c r="F299" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
+      <c r="G299" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
+      <c r="H299" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="n">
+      <c r="A300" s="31" t="n">
         <v>299</v>
       </c>
-      <c r="B300" t="n">
+      <c r="B300" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C300" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
+      <c r="D300" s="31" t="inlineStr">
         <is>
           <t>I burst from the ground in a fountain of steam, boiling and timed like the earth's own dream. What am I?</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
+      <c r="E300" s="31" t="inlineStr">
         <is>
           <t>A geyser</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
+      <c r="F300" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
+      <c r="G300" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
+      <c r="H300" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="n">
+      <c r="A301" s="31" t="n">
         <v>300</v>
       </c>
-      <c r="B301" t="n">
+      <c r="B301" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C301" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="D301" s="31" t="inlineStr">
         <is>
           <t>I twist from the sky in a funnel of wind, flinging up houses wherever I've been. What am I?</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
+      <c r="E301" s="31" t="inlineStr">
         <is>
           <t>A tornado</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
+      <c r="F301" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
+      <c r="G301" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
+      <c r="H301" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9870,7 +9870,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I204" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/MTHkkCmgI30</t>
         </is>
@@ -9910,7 +9910,12 @@
       </c>
       <c r="H205" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I205" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/9LlwNd3b1hA</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9953,12 @@
       </c>
       <c r="H206" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I206" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GAMolsA0JsE</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9996,12 @@
       </c>
       <c r="H207" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>https://youtu.be/K2G_B83QPyk</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -9999,7 +9999,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I207" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/K2G_B83QPyk</t>
         </is>
@@ -10039,7 +10039,12 @@
       </c>
       <c r="H208" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I208" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EeY_jDcgsDY</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10082,12 @@
       </c>
       <c r="H209" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I209" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/pAMpSCK8_kY</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10125,12 @@
       </c>
       <c r="H210" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>https://youtu.be/TmhzWpTaGGk</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10128,7 +10128,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I210" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/TmhzWpTaGGk</t>
         </is>
@@ -10168,7 +10168,12 @@
       </c>
       <c r="H211" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I211" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/PSUJ_u09Eos</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10211,12 @@
       </c>
       <c r="H212" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I212" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/zY0C4iOQznI</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10254,12 @@
       </c>
       <c r="H213" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aOidHmVbuSE</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10257,7 +10257,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
+      <c r="I213" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/aOidHmVbuSE</t>
         </is>
@@ -10297,7 +10297,12 @@
       </c>
       <c r="H214" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I214" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/0svh0kDimyI</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10340,12 @@
       </c>
       <c r="H215" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I215" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/NP7xq0Sw7Gk</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10383,12 @@
       </c>
       <c r="H216" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8uM3-KMh3Ns</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10386,7 +10386,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
+      <c r="I216" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/8uM3-KMh3Ns</t>
         </is>
@@ -10426,7 +10426,12 @@
       </c>
       <c r="H217" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I217" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/-OmK7moueTc</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10469,12 @@
       </c>
       <c r="H218" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I218" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/4659irnOcE8</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10512,12 @@
       </c>
       <c r="H219" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EhHGt9rsRJk</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10515,7 +10515,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I219" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/EhHGt9rsRJk</t>
         </is>
@@ -10555,7 +10555,12 @@
       </c>
       <c r="H220" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I220" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/_4-6HKL3uUQ</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10598,12 @@
       </c>
       <c r="H221" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I221" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/F8tbSv8faN8</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10641,12 @@
       </c>
       <c r="H222" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aHjhReY40yY</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10644,7 +10644,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="I222" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/aHjhReY40yY</t>
         </is>
@@ -10684,7 +10684,12 @@
       </c>
       <c r="H223" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I223" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/y-pPN2kODG4</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10727,12 @@
       </c>
       <c r="H224" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I224" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/q1JFTeqvzBk</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10770,12 @@
       </c>
       <c r="H225" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VMS0jMQX17A</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10773,7 +10773,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
+      <c r="I225" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/VMS0jMQX17A</t>
         </is>
@@ -10813,7 +10813,12 @@
       </c>
       <c r="H226" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I226" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/0L_C5kh5P6Q</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10856,12 @@
       </c>
       <c r="H227" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I227" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GKfhHdTJPiA</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10899,12 @@
       </c>
       <c r="H228" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UXnsVHH0Uz8</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -10902,7 +10902,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
+      <c r="I228" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/UXnsVHH0Uz8</t>
         </is>
@@ -10942,7 +10942,12 @@
       </c>
       <c r="H229" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I229" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/TCD_JcdrIa4</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10985,12 @@
       </c>
       <c r="H230" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I230" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/-w8CuUwK544</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11028,12 @@
       </c>
       <c r="H231" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VV06WYGv3Oo</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11031,7 +11031,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="I231" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/VV06WYGv3Oo</t>
         </is>
@@ -11071,7 +11071,12 @@
       </c>
       <c r="H232" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I232" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/aOxOTHa0GHo</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11114,12 @@
       </c>
       <c r="H233" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I233" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/SDNHb0sAYvQ</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11157,12 @@
       </c>
       <c r="H234" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>https://youtu.be/9CHdvvw63WM</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11160,7 +11160,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="I234" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/9CHdvvw63WM</t>
         </is>
@@ -11200,7 +11200,12 @@
       </c>
       <c r="H235" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I235" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7hyFIJzLm58</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11243,12 @@
       </c>
       <c r="H236" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I236" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/AqGrgfs1UEE</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11286,12 @@
       </c>
       <c r="H237" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UBPaZSLj_cE</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11289,7 +11289,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
+      <c r="I237" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/UBPaZSLj_cE</t>
         </is>
@@ -11329,7 +11329,12 @@
       </c>
       <c r="H238" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I238" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/mOJ3sPyG_XI</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11372,12 @@
       </c>
       <c r="H239" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I239" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/pCLu1T3S1io</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11415,12 @@
       </c>
       <c r="H240" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>https://youtu.be/1iymKAo3Roc</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11418,7 +11418,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
+      <c r="I240" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/1iymKAo3Roc</t>
         </is>
@@ -11458,7 +11458,12 @@
       </c>
       <c r="H241" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I241" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rj4XgKRFDAk</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11501,12 @@
       </c>
       <c r="H242" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I242" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/XRyRivlqQOI</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11544,12 @@
       </c>
       <c r="H243" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>https://youtu.be/-1vvQpC_Sc0</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11547,7 +11547,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
+      <c r="I243" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/-1vvQpC_Sc0</t>
         </is>
@@ -11587,7 +11587,12 @@
       </c>
       <c r="H244" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I244" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/F28Iw4HY64o</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11630,12 @@
       </c>
       <c r="H245" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I245" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/SI-WBMEOYSI</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11673,12 @@
       </c>
       <c r="H246" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>https://youtu.be/j6NAC1lVkB4</t>
         </is>
       </c>
     </row>
